--- a/data/ready_stocks/td-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/td-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B135"/>
+  <dimension ref="A1:B165"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -412,7 +412,7 @@
         <v>2043245296041</v>
       </c>
       <c r="B2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -420,7 +420,7 @@
         <v>2043245296065</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -428,7 +428,7 @@
         <v>2043245296157</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -436,7 +436,7 @@
         <v>2043245296171</v>
       </c>
       <c r="B5">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -444,7 +444,7 @@
         <v>2043245295358</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -452,7 +452,7 @@
         <v>2043245295365</v>
       </c>
       <c r="B7">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -460,7 +460,7 @@
         <v>2043245295266</v>
       </c>
       <c r="B8">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -468,7 +468,7 @@
         <v>2043245295440</v>
       </c>
       <c r="B9">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -476,7 +476,7 @@
         <v>2043245295464</v>
       </c>
       <c r="B10">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -492,7 +492,7 @@
         <v>2043245295532</v>
       </c>
       <c r="B12">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -508,7 +508,7 @@
         <v>2043245295570</v>
       </c>
       <c r="B14">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -524,7 +524,7 @@
         <v>2043245295594</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -532,7 +532,7 @@
         <v>2043245295600</v>
       </c>
       <c r="B17">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -548,7 +548,7 @@
         <v>2043245295822</v>
       </c>
       <c r="B19">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -556,20 +556,20 @@
         <v>2043245295877</v>
       </c>
       <c r="B20">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2043245295907</v>
+        <v>2043245295891</v>
       </c>
       <c r="B21">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2043245295938</v>
+        <v>2043245295907</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -577,47 +577,47 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2043245295983</v>
+        <v>2043245295938</v>
       </c>
       <c r="B23">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2043245295990</v>
+        <v>2043245295983</v>
       </c>
       <c r="B24">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2043245296058</v>
+        <v>2043245295990</v>
       </c>
       <c r="B25">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2043245296225</v>
+        <v>2043245296058</v>
       </c>
       <c r="B26">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2043245296287</v>
+        <v>2043245296225</v>
       </c>
       <c r="B27">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2043245296317</v>
+        <v>2043245296287</v>
       </c>
       <c r="B28">
         <v>5</v>
@@ -625,39 +625,39 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2043245296324</v>
+        <v>2043245296317</v>
       </c>
       <c r="B29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2043245296331</v>
+        <v>2043245296324</v>
       </c>
       <c r="B30">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2043245296348</v>
+        <v>2043245296331</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2043245296379</v>
+        <v>2043245296348</v>
       </c>
       <c r="B32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2043245296393</v>
+        <v>2043245296379</v>
       </c>
       <c r="B33">
         <v>5</v>
@@ -665,15 +665,15 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2043245296409</v>
+        <v>2043245296393</v>
       </c>
       <c r="B34">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2043245296416</v>
+        <v>2043245296409</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2043245296430</v>
+        <v>2043245296416</v>
       </c>
       <c r="B36">
         <v>5</v>
@@ -689,15 +689,15 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2043245296447</v>
+        <v>2043245296430</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2043245296454</v>
+        <v>2043245296447</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2043245296461</v>
+        <v>2043245296454</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -713,39 +713,39 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2043245295945</v>
+        <v>2043245296461</v>
       </c>
       <c r="B40">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2043245295815</v>
+        <v>2043245295389</v>
       </c>
       <c r="B41">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2043245295556</v>
+        <v>2043245295945</v>
       </c>
       <c r="B42">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2043245296027</v>
+        <v>2043245295815</v>
       </c>
       <c r="B43">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2043245296270</v>
+        <v>2043245295556</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2043245296362</v>
+        <v>2043245296027</v>
       </c>
       <c r="B45">
         <v>5</v>
@@ -761,39 +761,39 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2043245295846</v>
+        <v>2043245296270</v>
       </c>
       <c r="B46">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2043245296133</v>
+        <v>2043245296362</v>
       </c>
       <c r="B47">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2043245296423</v>
+        <v>2043245295846</v>
       </c>
       <c r="B48">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2043245296140</v>
+        <v>2043245296133</v>
       </c>
       <c r="B49">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2043245295273</v>
+        <v>2043245296423</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2043245295914</v>
+        <v>2043245296140</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -809,15 +809,15 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2043245295976</v>
+        <v>2043245295273</v>
       </c>
       <c r="B52">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2043245296195</v>
+        <v>2043245295914</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2043802980062</v>
+        <v>2043245295976</v>
       </c>
       <c r="B54">
         <v>5</v>
@@ -833,47 +833,47 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2043802980116</v>
+        <v>2043245296195</v>
       </c>
       <c r="B55">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2043802980130</v>
+        <v>2043802980062</v>
       </c>
       <c r="B56">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2043802980161</v>
+        <v>2043802980116</v>
       </c>
       <c r="B57">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2043802980178</v>
+        <v>2043802980130</v>
       </c>
       <c r="B58">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2043802980208</v>
+        <v>2043802980161</v>
       </c>
       <c r="B59">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2043802980246</v>
+        <v>2043802980178</v>
       </c>
       <c r="B60">
         <v>5</v>
@@ -881,39 +881,39 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2043802980253</v>
+        <v>2043802980208</v>
       </c>
       <c r="B61">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2043802980260</v>
+        <v>2043802980246</v>
       </c>
       <c r="B62">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2043802980277</v>
+        <v>2043802980253</v>
       </c>
       <c r="B63">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2043802980307</v>
+        <v>2043802980260</v>
       </c>
       <c r="B64">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2043245295372</v>
+        <v>2043802980277</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -921,31 +921,31 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2043245295426</v>
+        <v>2043802980307</v>
       </c>
       <c r="B66">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2043245295860</v>
+        <v>2043245295372</v>
       </c>
       <c r="B67">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2043245295921</v>
+        <v>2043245295426</v>
       </c>
       <c r="B68">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2043245295242</v>
+        <v>2043245295860</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -953,39 +953,39 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2043245295785</v>
+        <v>2043245295921</v>
       </c>
       <c r="B70">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2043245295969</v>
+        <v>2043245295242</v>
       </c>
       <c r="B71">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2043245295396</v>
+        <v>2043245295785</v>
       </c>
       <c r="B72">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2043245295402</v>
+        <v>2043245295969</v>
       </c>
       <c r="B73">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2043343781258</v>
+        <v>2043245295396</v>
       </c>
       <c r="B74">
         <v>5</v>
@@ -993,15 +993,15 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2043343781500</v>
+        <v>2043245295402</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2043343780893</v>
+        <v>2043343781258</v>
       </c>
       <c r="B76">
         <v>5</v>
@@ -1009,71 +1009,71 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2043343780909</v>
+        <v>2043343781500</v>
       </c>
       <c r="B77">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2043343780916</v>
+        <v>2043343780893</v>
       </c>
       <c r="B78">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2043343780947</v>
+        <v>2043343780909</v>
       </c>
       <c r="B79">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2043343780954</v>
+        <v>2043343780916</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2043343780978</v>
+        <v>2043343780947</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2043343781036</v>
+        <v>2043343780954</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2043343781043</v>
+        <v>2043343780978</v>
       </c>
       <c r="B83">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2043343781067</v>
+        <v>2043343781036</v>
       </c>
       <c r="B84">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2043343781074</v>
+        <v>2043343781043</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2043343781081</v>
+        <v>2043343781067</v>
       </c>
       <c r="B86">
         <v>5</v>
@@ -1089,23 +1089,23 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2043343781098</v>
+        <v>2043343781074</v>
       </c>
       <c r="B87">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2043343781104</v>
+        <v>2043343781081</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2043343781111</v>
+        <v>2043343781098</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1113,23 +1113,23 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2043343781128</v>
+        <v>2043343781104</v>
       </c>
       <c r="B90">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2043343781135</v>
+        <v>2043343781111</v>
       </c>
       <c r="B91">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2043343781142</v>
+        <v>2043343781128</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1137,23 +1137,23 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2043343781159</v>
+        <v>2043343781135</v>
       </c>
       <c r="B93">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2043343781166</v>
+        <v>2043343781142</v>
       </c>
       <c r="B94">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2043343781173</v>
+        <v>2043343781159</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1161,23 +1161,23 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2043343781180</v>
+        <v>2043343781166</v>
       </c>
       <c r="B96">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2043343781333</v>
+        <v>2043343781173</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2043343781470</v>
+        <v>2043343781180</v>
       </c>
       <c r="B98">
         <v>5</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2043343781401</v>
+        <v>2043343781333</v>
       </c>
       <c r="B99">
         <v>5</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2043343781197</v>
+        <v>2043343781470</v>
       </c>
       <c r="B100">
         <v>5</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2043343781203</v>
+        <v>2043343781401</v>
       </c>
       <c r="B101">
         <v>5</v>
@@ -1209,15 +1209,15 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2043343781227</v>
+        <v>2043343781197</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2043343781234</v>
+        <v>2043343781203</v>
       </c>
       <c r="B103">
         <v>5</v>
@@ -1225,15 +1225,15 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2043343781241</v>
+        <v>2043343781227</v>
       </c>
       <c r="B104">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2043343781265</v>
+        <v>2043343781234</v>
       </c>
       <c r="B105">
         <v>5</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2043343781272</v>
+        <v>2043343781241</v>
       </c>
       <c r="B106">
         <v>5</v>
@@ -1249,23 +1249,23 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2043343781289</v>
+        <v>2043343781265</v>
       </c>
       <c r="B107">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2043343781296</v>
+        <v>2043343781272</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2043343781319</v>
+        <v>2043343781289</v>
       </c>
       <c r="B109">
         <v>5</v>
@@ -1273,23 +1273,23 @@
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2043343781326</v>
+        <v>2043343781296</v>
       </c>
       <c r="B110">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2043343781340</v>
+        <v>2043343781319</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2043343781357</v>
+        <v>2043343781326</v>
       </c>
       <c r="B112">
         <v>5</v>
@@ -1297,15 +1297,15 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2043343781364</v>
+        <v>2043343781340</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2043343781371</v>
+        <v>2043343781357</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2043343781388</v>
+        <v>2043343781364</v>
       </c>
       <c r="B115">
         <v>5</v>
@@ -1321,23 +1321,23 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2043343781395</v>
+        <v>2043343781371</v>
       </c>
       <c r="B116">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2043343781418</v>
+        <v>2043343781388</v>
       </c>
       <c r="B117">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2043343781425</v>
+        <v>2043343781395</v>
       </c>
       <c r="B118">
         <v>5</v>
@@ -1345,15 +1345,15 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2043343781432</v>
+        <v>2043343781418</v>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2043343781449</v>
+        <v>2043343781425</v>
       </c>
       <c r="B120">
         <v>5</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2043343781555</v>
+        <v>2043343781432</v>
       </c>
       <c r="B121">
         <v>5</v>
@@ -1369,15 +1369,15 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2043343781463</v>
+        <v>2043343781449</v>
       </c>
       <c r="B122">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2043343781487</v>
+        <v>2043343781555</v>
       </c>
       <c r="B123">
         <v>5</v>
@@ -1385,7 +1385,7 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2043343781548</v>
+        <v>2043343781463</v>
       </c>
       <c r="B124">
         <v>5</v>
@@ -1393,15 +1393,15 @@
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2043343781494</v>
+        <v>2043343781487</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2043343780992</v>
+        <v>2043343781548</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,23 +1409,23 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2043343781302</v>
+        <v>2043343781494</v>
       </c>
       <c r="B127">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2043343781456</v>
+        <v>2043343780992</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2043343781531</v>
+        <v>2043343781302</v>
       </c>
       <c r="B129">
         <v>5</v>
@@ -1433,7 +1433,7 @@
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2043343781524</v>
+        <v>2043343781456</v>
       </c>
       <c r="B130">
         <v>5</v>
@@ -1441,7 +1441,7 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2043343781517</v>
+        <v>2043343781531</v>
       </c>
       <c r="B131">
         <v>0</v>
@@ -1449,7 +1449,7 @@
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2043343781586</v>
+        <v>2043343781524</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2043343781579</v>
+        <v>2043343781517</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2043343781562</v>
+        <v>2043343781586</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1473,15 +1473,255 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
+        <v>2043343781579</v>
+      </c>
+      <c r="B135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>2043343781562</v>
+      </c>
+      <c r="B136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
         <v>2043343781210</v>
       </c>
-      <c r="B135">
+      <c r="B137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>2046921819367</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>2046921819299</v>
+      </c>
+      <c r="B139">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>2046921819282</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>2046921819626</v>
+      </c>
+      <c r="B141">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>2046921819565</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>2046921819510</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>2046921819343</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>2046921819329</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>2046921819558</v>
+      </c>
+      <c r="B146">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>2046921819527</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>2046921819480</v>
+      </c>
+      <c r="B148">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>2046921819411</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>2046921819435</v>
+      </c>
+      <c r="B150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>2046920701731</v>
+      </c>
+      <c r="B151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>2046921819657</v>
+      </c>
+      <c r="B152">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>2046921819596</v>
+      </c>
+      <c r="B153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>2046921819404</v>
+      </c>
+      <c r="B154">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>2046921671828</v>
+      </c>
+      <c r="B155">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>2046921819466</v>
+      </c>
+      <c r="B156">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>2046921819305</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>2046921819541</v>
+      </c>
+      <c r="B158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>2046921819503</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>2046921819398</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>2046921819350</v>
+      </c>
+      <c r="B161">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>2046921819381</v>
+      </c>
+      <c r="B162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>2046921819312</v>
+      </c>
+      <c r="B163">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>2046921819336</v>
+      </c>
+      <c r="B164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>2046921819473</v>
+      </c>
+      <c r="B165">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B135"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B165"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/td-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/td-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B165"/>
+  <dimension ref="A1:B352"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -988,7 +988,7 @@
         <v>2043245295396</v>
       </c>
       <c r="B74">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1496,232 +1496,1728 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="str">
+      <c r="A138">
+        <v>2044717717149</v>
+      </c>
+      <c r="B138">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>2044717717132</v>
+      </c>
+      <c r="B139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>2044717717385</v>
+      </c>
+      <c r="B140">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>2044717717125</v>
+      </c>
+      <c r="B141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>2044717717293</v>
+      </c>
+      <c r="B142">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>2044717717187</v>
+      </c>
+      <c r="B143">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>2044717717316</v>
+      </c>
+      <c r="B144">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>2044717717330</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>2044717717064</v>
+      </c>
+      <c r="B146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>2044717717200</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>2044717717231</v>
+      </c>
+      <c r="B148">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>2044717717156</v>
+      </c>
+      <c r="B149">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>2044717717101</v>
+      </c>
+      <c r="B150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>2044717717446</v>
+      </c>
+      <c r="B151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>2044717717118</v>
+      </c>
+      <c r="B152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>2044717717248</v>
+      </c>
+      <c r="B153">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>2044717717422</v>
+      </c>
+      <c r="B154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>2044717717170</v>
+      </c>
+      <c r="B155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>2044717717354</v>
+      </c>
+      <c r="B156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>2044717717460</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>2044717717224</v>
+      </c>
+      <c r="B158">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>2044717717071</v>
+      </c>
+      <c r="B159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160">
+        <v>2044717717088</v>
+      </c>
+      <c r="B160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>2044717717194</v>
+      </c>
+      <c r="B161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>2044717717378</v>
+      </c>
+      <c r="B162">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>2044717717095</v>
+      </c>
+      <c r="B163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>2044717717484</v>
+      </c>
+      <c r="B164">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>2044715906811</v>
+      </c>
+      <c r="B165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>2044715906835</v>
+      </c>
+      <c r="B166">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>2044715906842</v>
+      </c>
+      <c r="B167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>2044715906859</v>
+      </c>
+      <c r="B168">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>2044715906866</v>
+      </c>
+      <c r="B169">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>2044715906873</v>
+      </c>
+      <c r="B170">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>2044715906880</v>
+      </c>
+      <c r="B171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>2044715906897</v>
+      </c>
+      <c r="B172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>2044715906903</v>
+      </c>
+      <c r="B173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2044715906910</v>
+      </c>
+      <c r="B174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2044715906927</v>
+      </c>
+      <c r="B175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2044715906934</v>
+      </c>
+      <c r="B176">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2044715906958</v>
+      </c>
+      <c r="B177">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>2044715906965</v>
+      </c>
+      <c r="B178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2044715906972</v>
+      </c>
+      <c r="B179">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2044715906989</v>
+      </c>
+      <c r="B180">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2044715906996</v>
+      </c>
+      <c r="B181">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>2044715907009</v>
+      </c>
+      <c r="B182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2044715907023</v>
+      </c>
+      <c r="B183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>2044715907030</v>
+      </c>
+      <c r="B184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>2044715905807</v>
+      </c>
+      <c r="B185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>2044715905821</v>
+      </c>
+      <c r="B186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>2044715905838</v>
+      </c>
+      <c r="B187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>2044715905852</v>
+      </c>
+      <c r="B188">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>2044715905869</v>
+      </c>
+      <c r="B189">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2044715905876</v>
+      </c>
+      <c r="B190">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>2044715905883</v>
+      </c>
+      <c r="B191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>2044715905906</v>
+      </c>
+      <c r="B192">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>2044715905913</v>
+      </c>
+      <c r="B193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>2044715905920</v>
+      </c>
+      <c r="B194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>2044715905944</v>
+      </c>
+      <c r="B195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>2044715905951</v>
+      </c>
+      <c r="B196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>2044715905968</v>
+      </c>
+      <c r="B197">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>2044715905982</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>2044715905999</v>
+      </c>
+      <c r="B199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>2044715906002</v>
+      </c>
+      <c r="B200">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>2044715906019</v>
+      </c>
+      <c r="B201">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>2044715906026</v>
+      </c>
+      <c r="B202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>2044715906040</v>
+      </c>
+      <c r="B203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>2044715906057</v>
+      </c>
+      <c r="B204">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>2044715906071</v>
+      </c>
+      <c r="B205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>2044715906088</v>
+      </c>
+      <c r="B206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>2044715906095</v>
+      </c>
+      <c r="B207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>2044715906101</v>
+      </c>
+      <c r="B208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>2044715906118</v>
+      </c>
+      <c r="B209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>2044715906125</v>
+      </c>
+      <c r="B210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>2044715906132</v>
+      </c>
+      <c r="B211">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>2044715906545</v>
+      </c>
+      <c r="B212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>2044715906552</v>
+      </c>
+      <c r="B213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>2044715906569</v>
+      </c>
+      <c r="B214">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>2044715906576</v>
+      </c>
+      <c r="B215">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>2044715906583</v>
+      </c>
+      <c r="B216">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>2044715906590</v>
+      </c>
+      <c r="B217">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>2044715906606</v>
+      </c>
+      <c r="B218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>2044715906613</v>
+      </c>
+      <c r="B219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>2044715906637</v>
+      </c>
+      <c r="B220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>2044715906644</v>
+      </c>
+      <c r="B221">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>2044715906668</v>
+      </c>
+      <c r="B222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>2044715906675</v>
+      </c>
+      <c r="B223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>2044715906682</v>
+      </c>
+      <c r="B224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225">
+        <v>2044715906699</v>
+      </c>
+      <c r="B225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226">
+        <v>2044715906705</v>
+      </c>
+      <c r="B226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227">
+        <v>2044715906729</v>
+      </c>
+      <c r="B227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228">
+        <v>2044715906736</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229">
+        <v>2044715906743</v>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230">
+        <v>2044715906767</v>
+      </c>
+      <c r="B230">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231">
+        <v>2044715906798</v>
+      </c>
+      <c r="B231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232">
+        <v>2044719078644</v>
+      </c>
+      <c r="B232">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233">
+        <v>2044719078736</v>
+      </c>
+      <c r="B233">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234">
+        <v>2044719078040</v>
+      </c>
+      <c r="B234">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235">
+        <v>2044719078590</v>
+      </c>
+      <c r="B235">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>2044719078514</v>
+      </c>
+      <c r="B236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>2044719078842</v>
+      </c>
+      <c r="B237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>2044719079009</v>
+      </c>
+      <c r="B238">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>2044719078217</v>
+      </c>
+      <c r="B239">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>2044719078804</v>
+      </c>
+      <c r="B240">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>2044719079047</v>
+      </c>
+      <c r="B241">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>2044719078460</v>
+      </c>
+      <c r="B242">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>2044719078125</v>
+      </c>
+      <c r="B243">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>2044719078170</v>
+      </c>
+      <c r="B244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>2044719078477</v>
+      </c>
+      <c r="B245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>2044719078507</v>
+      </c>
+      <c r="B246">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>2044719078705</v>
+      </c>
+      <c r="B247">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>2044719079023</v>
+      </c>
+      <c r="B248">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>2044719078835</v>
+      </c>
+      <c r="B249">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>2044719078484</v>
+      </c>
+      <c r="B250">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>2044719078965</v>
+      </c>
+      <c r="B251">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>2044719079016</v>
+      </c>
+      <c r="B252">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>2044719078255</v>
+      </c>
+      <c r="B253">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>2044719078668</v>
+      </c>
+      <c r="B254">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>2044719078088</v>
+      </c>
+      <c r="B255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>2044719078491</v>
+      </c>
+      <c r="B256">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>2044719078651</v>
+      </c>
+      <c r="B257">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>2044719078620</v>
+      </c>
+      <c r="B258">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>2044719078712</v>
+      </c>
+      <c r="B259">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>2044719079030</v>
+      </c>
+      <c r="B260">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>2044719078200</v>
+      </c>
+      <c r="B261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>2044719078828</v>
+      </c>
+      <c r="B262">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>2044719078538</v>
+      </c>
+      <c r="B263">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>2044719078972</v>
+      </c>
+      <c r="B264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>2044719078866</v>
+      </c>
+      <c r="B265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>2044719078613</v>
+      </c>
+      <c r="B266">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>2044719078071</v>
+      </c>
+      <c r="B267">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>2044719078132</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>2044719078446</v>
+      </c>
+      <c r="B269">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>2044719078163</v>
+      </c>
+      <c r="B270">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>2044719078873</v>
+      </c>
+      <c r="B271">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>2044719078729</v>
+      </c>
+      <c r="B272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>2044719078743</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>2044719078569</v>
+      </c>
+      <c r="B274">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>2044719078248</v>
+      </c>
+      <c r="B275">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>2044719078903</v>
+      </c>
+      <c r="B276">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>2044719078156</v>
+      </c>
+      <c r="B277">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>2044719078781</v>
+      </c>
+      <c r="B278">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>2044719078996</v>
+      </c>
+      <c r="B279">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>2044719078699</v>
+      </c>
+      <c r="B280">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>2044719078439</v>
+      </c>
+      <c r="B281">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>2044719078583</v>
+      </c>
+      <c r="B282">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>2044719078545</v>
+      </c>
+      <c r="B283">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>2044719078989</v>
+      </c>
+      <c r="B284">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>2044719078231</v>
+      </c>
+      <c r="B285">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>2044719078941</v>
+      </c>
+      <c r="B286">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>2044719078453</v>
+      </c>
+      <c r="B287">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>2044719078897</v>
+      </c>
+      <c r="B288">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>2044719078118</v>
+      </c>
+      <c r="B289">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>2044719078576</v>
+      </c>
+      <c r="B290">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>2044719078194</v>
+      </c>
+      <c r="B291">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>2044719078774</v>
+      </c>
+      <c r="B292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293">
+        <v>2044719078149</v>
+      </c>
+      <c r="B293">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>2044719078187</v>
+      </c>
+      <c r="B294">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>2044719078859</v>
+      </c>
+      <c r="B295">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>2044719078064</v>
+      </c>
+      <c r="B296">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>2044719078750</v>
+      </c>
+      <c r="B297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>2044719078880</v>
+      </c>
+      <c r="B298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>2044719078057</v>
+      </c>
+      <c r="B299">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>2044719078224</v>
+      </c>
+      <c r="B300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>2044661682678</v>
+      </c>
+      <c r="B301">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>2044661682753</v>
+      </c>
+      <c r="B302">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>2044661682715</v>
+      </c>
+      <c r="B303">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>2044661682814</v>
+      </c>
+      <c r="B304">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>2044661682425</v>
+      </c>
+      <c r="B305">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>2044661682654</v>
+      </c>
+      <c r="B306">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>2044661682708</v>
+      </c>
+      <c r="B307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>2044661682548</v>
+      </c>
+      <c r="B308">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>2044661682487</v>
+      </c>
+      <c r="B309">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>2044661682456</v>
+      </c>
+      <c r="B310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>2044661682784</v>
+      </c>
+      <c r="B311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>2044661682463</v>
+      </c>
+      <c r="B312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>2044661682524</v>
+      </c>
+      <c r="B313">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>2044661682623</v>
+      </c>
+      <c r="B314">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>2044661682777</v>
+      </c>
+      <c r="B315">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>2044661682593</v>
+      </c>
+      <c r="B316">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>2044661682449</v>
+      </c>
+      <c r="B317">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>2044661682500</v>
+      </c>
+      <c r="B318">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>2044661682739</v>
+      </c>
+      <c r="B319">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>2044661682685</v>
+      </c>
+      <c r="B320">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>2044661682616</v>
+      </c>
+      <c r="B321">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>2044661682791</v>
+      </c>
+      <c r="B322">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>2044661682586</v>
+      </c>
+      <c r="B323">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>2044661682562</v>
+      </c>
+      <c r="B324">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
         <v>2046921819367</v>
       </c>
-      <c r="B138">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="str">
+      <c r="B325">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
         <v>2046921819299</v>
       </c>
-      <c r="B139">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="str">
+      <c r="B326">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
         <v>2046921819282</v>
       </c>
-      <c r="B140">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="str">
+      <c r="B327">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
         <v>2046921819626</v>
       </c>
-      <c r="B141">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="str">
+      <c r="B328">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
         <v>2046921819565</v>
       </c>
-      <c r="B142">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="str">
+      <c r="B329">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
         <v>2046921819510</v>
       </c>
-      <c r="B143">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="str">
+      <c r="B330">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
         <v>2046921819343</v>
       </c>
-      <c r="B144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="str">
+      <c r="B331">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
         <v>2046921819329</v>
       </c>
-      <c r="B145">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="str">
+      <c r="B332">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
         <v>2046921819558</v>
       </c>
-      <c r="B146">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="str">
+      <c r="B333">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
         <v>2046921819527</v>
       </c>
-      <c r="B147">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="str">
+      <c r="B334">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
         <v>2046921819480</v>
       </c>
-      <c r="B148">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="str">
+      <c r="B335">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
         <v>2046921819411</v>
       </c>
-      <c r="B149">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="str">
+      <c r="B336">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
         <v>2046921819435</v>
       </c>
-      <c r="B150">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="str">
+      <c r="B337">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
         <v>2046920701731</v>
       </c>
-      <c r="B151">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="str">
+      <c r="B338">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
         <v>2046921819657</v>
       </c>
-      <c r="B152">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="str">
+      <c r="B339">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
         <v>2046921819596</v>
       </c>
-      <c r="B153">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="str">
+      <c r="B340">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
         <v>2046921819404</v>
       </c>
-      <c r="B154">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="str">
+      <c r="B341">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
         <v>2046921671828</v>
       </c>
-      <c r="B155">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="str">
+      <c r="B342">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
         <v>2046921819466</v>
       </c>
-      <c r="B156">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="str">
+      <c r="B343">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
         <v>2046921819305</v>
       </c>
-      <c r="B157">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="str">
+      <c r="B344">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
         <v>2046921819541</v>
       </c>
-      <c r="B158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="str">
+      <c r="B345">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
         <v>2046921819503</v>
       </c>
-      <c r="B159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="str">
+      <c r="B346">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
         <v>2046921819398</v>
       </c>
-      <c r="B160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="str">
+      <c r="B347">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
         <v>2046921819350</v>
       </c>
-      <c r="B161">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="str">
+      <c r="B348">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
         <v>2046921819381</v>
       </c>
-      <c r="B162">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="str">
+      <c r="B349">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
         <v>2046921819312</v>
       </c>
-      <c r="B163">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="str">
+      <c r="B350">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
         <v>2046921819336</v>
       </c>
-      <c r="B164">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="str">
+      <c r="B351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
         <v>2046921819473</v>
       </c>
-      <c r="B165">
+      <c r="B352">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B165"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B352"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/ready_stocks/td-wb-stocks-updated.xlsx
+++ b/data/ready_stocks/td-wb-stocks-updated.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B573"/>
+  <dimension ref="A1:B572"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,7 +409,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>2043245296041</v>
+        <v>2043245296065</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -417,7 +417,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2043245296065</v>
+        <v>2043245296157</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -425,7 +425,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>2043245296157</v>
+        <v>2043245296171</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -433,7 +433,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>2043245296171</v>
+        <v>2043245295358</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -441,7 +441,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2043245295358</v>
+        <v>2043245295365</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -449,7 +449,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>2043245295365</v>
+        <v>2043245295266</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -457,7 +457,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2043245295266</v>
+        <v>2043245295440</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -465,7 +465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2043245295440</v>
+        <v>2043245295464</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -473,7 +473,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>2043245295464</v>
+        <v>2043245295471</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -481,7 +481,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>2043245295471</v>
+        <v>2043245295532</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -489,7 +489,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>2043245295532</v>
+        <v>2043245295563</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -497,7 +497,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>2043245295563</v>
+        <v>2043245295570</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -505,7 +505,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>2043245295570</v>
+        <v>2043245295587</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -513,7 +513,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>2043245295587</v>
+        <v>2043245295594</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -521,7 +521,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>2043245295594</v>
+        <v>2043245295600</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>2043245295600</v>
+        <v>2043245295792</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -537,7 +537,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>2043245295792</v>
+        <v>2043245295822</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -545,7 +545,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>2043245295822</v>
+        <v>2043245295877</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -553,7 +553,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>2043245295877</v>
+        <v>2043245295891</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>2043245295891</v>
+        <v>2043245295907</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -569,7 +569,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>2043245295907</v>
+        <v>2043245295938</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -577,7 +577,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>2043245295938</v>
+        <v>2043245295983</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>2043245295983</v>
+        <v>2043245295990</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -593,7 +593,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>2043245295990</v>
+        <v>2043245296058</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -601,7 +601,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>2043245296058</v>
+        <v>2043245296225</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>2043245296225</v>
+        <v>2043245296287</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -617,7 +617,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>2043245296287</v>
+        <v>2043245296317</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -625,7 +625,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>2043245296317</v>
+        <v>2043245296324</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -633,23 +633,23 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>2043245296324</v>
+        <v>2043245296331</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>2043245296331</v>
+        <v>2043245296348</v>
       </c>
       <c r="B31">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>2043245296348</v>
+        <v>2043245296379</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -657,7 +657,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>2043245296379</v>
+        <v>2043245296393</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -665,7 +665,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>2043245296393</v>
+        <v>2043245296409</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -673,7 +673,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>2043245296409</v>
+        <v>2043245296416</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -681,7 +681,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>2043245296416</v>
+        <v>2043245296430</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>2043245296430</v>
+        <v>2043245296447</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>2043245296447</v>
+        <v>2043245296454</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -705,7 +705,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>2043245296454</v>
+        <v>2043245296461</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>2043245296461</v>
+        <v>2043245295389</v>
       </c>
       <c r="B40">
         <v>0</v>
@@ -721,7 +721,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>2043245295389</v>
+        <v>2043245295945</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -729,7 +729,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>2043245295945</v>
+        <v>2043245295815</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>2043245295815</v>
+        <v>2043245295556</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -745,7 +745,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>2043245295556</v>
+        <v>2043245296027</v>
       </c>
       <c r="B44">
         <v>0</v>
@@ -753,15 +753,15 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>2043245296027</v>
+        <v>2043245296270</v>
       </c>
       <c r="B45">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>2043245296270</v>
+        <v>2043245296362</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -769,7 +769,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>2043245296362</v>
+        <v>2043245295846</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>2043245295846</v>
+        <v>2043245296133</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>2043245296133</v>
+        <v>2043245296423</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -793,7 +793,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>2043245296423</v>
+        <v>2043245296140</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -801,7 +801,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>2043245296140</v>
+        <v>2043245295273</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>2043245295273</v>
+        <v>2043245295914</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -817,7 +817,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>2043245295914</v>
+        <v>2043245295976</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -825,7 +825,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>2043245295976</v>
+        <v>2043245296195</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -833,7 +833,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>2043245296195</v>
+        <v>2043802980062</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -841,7 +841,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>2043802980062</v>
+        <v>2043802980116</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -849,7 +849,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>2043802980116</v>
+        <v>2043802980130</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -857,15 +857,15 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>2043802980130</v>
+        <v>2043802980161</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>2043802980161</v>
+        <v>2043802980178</v>
       </c>
       <c r="B59">
         <v>5</v>
@@ -873,15 +873,15 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>2043802980178</v>
+        <v>2043802980208</v>
       </c>
       <c r="B60">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>2043802980208</v>
+        <v>2043802980246</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -889,7 +889,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>2043802980246</v>
+        <v>2043802980253</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -897,7 +897,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>2043802980253</v>
+        <v>2043802980260</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -905,7 +905,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>2043802980260</v>
+        <v>2043802980277</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -913,7 +913,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>2043802980277</v>
+        <v>2043802980307</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>2043802980307</v>
+        <v>2043802980291</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>2043802980291</v>
+        <v>2043245295372</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -937,7 +937,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>2043245295372</v>
+        <v>2043245295426</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>2043245295426</v>
+        <v>2043245295860</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -953,7 +953,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>2043245295860</v>
+        <v>2043245295921</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -961,7 +961,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>2043245295921</v>
+        <v>2043245295242</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -969,7 +969,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>2043245295242</v>
+        <v>2043245295785</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>2043245295785</v>
+        <v>2043245295969</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -985,7 +985,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>2043245295969</v>
+        <v>2043245295396</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -993,23 +993,23 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>2043245295396</v>
+        <v>2043245295402</v>
       </c>
       <c r="B75">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>2043245295402</v>
+        <v>2043343781258</v>
       </c>
       <c r="B76">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>2043343781258</v>
+        <v>2043343781500</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -1017,7 +1017,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>2043343781500</v>
+        <v>2043343780893</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>2043343780893</v>
+        <v>2043343780909</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -1033,23 +1033,23 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>2043343780909</v>
+        <v>2043343780916</v>
       </c>
       <c r="B80">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>2043343780916</v>
+        <v>2043343780947</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>2043343780947</v>
+        <v>2043343780954</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -1057,7 +1057,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>2043343780954</v>
+        <v>2043343780978</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -1065,7 +1065,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>2043343780978</v>
+        <v>2043343781036</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>2043343781036</v>
+        <v>2043343781043</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>2043343781043</v>
+        <v>2043343781067</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -1089,23 +1089,23 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>2043343781067</v>
+        <v>2043343781074</v>
       </c>
       <c r="B87">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>2043343781074</v>
+        <v>2043343781081</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>2043343781081</v>
+        <v>2043343781098</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>2043343781098</v>
+        <v>2043343781104</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -1121,7 +1121,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>2043343781104</v>
+        <v>2043343781111</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -1129,7 +1129,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>2043343781111</v>
+        <v>2043343781128</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>2043343781128</v>
+        <v>2043343781135</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>2043343781135</v>
+        <v>2043343781142</v>
       </c>
       <c r="B94">
         <v>0</v>
@@ -1153,7 +1153,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>2043343781142</v>
+        <v>2043343781159</v>
       </c>
       <c r="B95">
         <v>0</v>
@@ -1161,7 +1161,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>2043343781159</v>
+        <v>2043343781166</v>
       </c>
       <c r="B96">
         <v>0</v>
@@ -1169,7 +1169,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>2043343781166</v>
+        <v>2043343781173</v>
       </c>
       <c r="B97">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>2043343781173</v>
+        <v>2043343781180</v>
       </c>
       <c r="B98">
         <v>0</v>
@@ -1185,31 +1185,31 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>2043343781180</v>
+        <v>2043343781333</v>
       </c>
       <c r="B99">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>2043343781333</v>
+        <v>2043343781470</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>2043343781470</v>
+        <v>2043343781401</v>
       </c>
       <c r="B101">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>2043343781401</v>
+        <v>2043343781197</v>
       </c>
       <c r="B102">
         <v>5</v>
@@ -1217,15 +1217,15 @@
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>2043343781197</v>
+        <v>2043343781203</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>2043343781203</v>
+        <v>2043343781227</v>
       </c>
       <c r="B104">
         <v>0</v>
@@ -1233,7 +1233,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>2043343781227</v>
+        <v>2043343781234</v>
       </c>
       <c r="B105">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>2043343781234</v>
+        <v>2043343781241</v>
       </c>
       <c r="B106">
         <v>0</v>
@@ -1249,15 +1249,15 @@
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>2043343781241</v>
+        <v>2043343781265</v>
       </c>
       <c r="B107">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>2043343781265</v>
+        <v>2043343781272</v>
       </c>
       <c r="B108">
         <v>5</v>
@@ -1265,47 +1265,47 @@
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>2043343781272</v>
+        <v>2043343781289</v>
       </c>
       <c r="B109">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>2043343781289</v>
+        <v>2043343781296</v>
       </c>
       <c r="B110">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>2043343781296</v>
+        <v>2043343781319</v>
       </c>
       <c r="B111">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>2043343781319</v>
+        <v>2043343781326</v>
       </c>
       <c r="B112">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>2043343781326</v>
+        <v>2043343781340</v>
       </c>
       <c r="B113">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>2043343781340</v>
+        <v>2043343781357</v>
       </c>
       <c r="B114">
         <v>0</v>
@@ -1313,7 +1313,7 @@
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>2043343781357</v>
+        <v>2043343781364</v>
       </c>
       <c r="B115">
         <v>0</v>
@@ -1321,7 +1321,7 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>2043343781364</v>
+        <v>2043343781371</v>
       </c>
       <c r="B116">
         <v>0</v>
@@ -1329,7 +1329,7 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>2043343781371</v>
+        <v>2043343781388</v>
       </c>
       <c r="B117">
         <v>0</v>
@@ -1337,23 +1337,23 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>2043343781388</v>
+        <v>2043343781395</v>
       </c>
       <c r="B118">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>2043343781395</v>
+        <v>2043343781418</v>
       </c>
       <c r="B119">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>2043343781418</v>
+        <v>2043343781425</v>
       </c>
       <c r="B120">
         <v>0</v>
@@ -1361,15 +1361,15 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>2043343781425</v>
+        <v>2043343781432</v>
       </c>
       <c r="B121">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>2043343781432</v>
+        <v>2043343781449</v>
       </c>
       <c r="B122">
         <v>0</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>2043343781449</v>
+        <v>2043343781555</v>
       </c>
       <c r="B123">
         <v>0</v>
@@ -1385,23 +1385,23 @@
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>2043343781555</v>
+        <v>2043343781463</v>
       </c>
       <c r="B124">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>2043343781463</v>
+        <v>2043343781487</v>
       </c>
       <c r="B125">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>2043343781487</v>
+        <v>2043343781548</v>
       </c>
       <c r="B126">
         <v>0</v>
@@ -1409,31 +1409,31 @@
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>2043343781548</v>
+        <v>2043343781494</v>
       </c>
       <c r="B127">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>2043343781494</v>
+        <v>2043343780992</v>
       </c>
       <c r="B128">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>2043343780992</v>
+        <v>2043343781302</v>
       </c>
       <c r="B129">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>2043343781302</v>
+        <v>2043343781456</v>
       </c>
       <c r="B130">
         <v>5</v>
@@ -1441,15 +1441,15 @@
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>2043343781456</v>
+        <v>2043343781531</v>
       </c>
       <c r="B131">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>2043343781531</v>
+        <v>2043343781524</v>
       </c>
       <c r="B132">
         <v>0</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>2043343781524</v>
+        <v>2043343781517</v>
       </c>
       <c r="B133">
         <v>0</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>2043343781517</v>
+        <v>2043343781586</v>
       </c>
       <c r="B134">
         <v>0</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>2043343781586</v>
+        <v>2043343781579</v>
       </c>
       <c r="B135">
         <v>0</v>
@@ -1481,7 +1481,7 @@
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>2043343781579</v>
+        <v>2043343781562</v>
       </c>
       <c r="B136">
         <v>0</v>
@@ -1489,23 +1489,23 @@
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>2043343781562</v>
+        <v>2043343781210</v>
       </c>
       <c r="B137">
         <v>0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="str">
-        <v>2043343781210</v>
+      <c r="A138">
+        <v>2044717717149</v>
       </c>
       <c r="B138">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139">
       <c r="A139">
-        <v>2044717717149</v>
+        <v>2044717717132</v>
       </c>
       <c r="B139">
         <v>5</v>
@@ -1513,7 +1513,7 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>2044717717132</v>
+        <v>2044717717385</v>
       </c>
       <c r="B140">
         <v>5</v>
@@ -1521,31 +1521,31 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2044717717385</v>
+        <v>2044717717125</v>
       </c>
       <c r="B141">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142">
-        <v>2044717717125</v>
+        <v>2044717717293</v>
       </c>
       <c r="B142">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143">
       <c r="A143">
-        <v>2044717717293</v>
+        <v>2044717717187</v>
       </c>
       <c r="B143">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144">
-        <v>2044717717187</v>
+        <v>2044717717316</v>
       </c>
       <c r="B144">
         <v>0</v>
@@ -1553,87 +1553,87 @@
     </row>
     <row r="145">
       <c r="A145">
-        <v>2044717717316</v>
+        <v>2044717717330</v>
       </c>
       <c r="B145">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146">
       <c r="A146">
-        <v>2044717717330</v>
+        <v>2044717717064</v>
       </c>
       <c r="B146">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
       <c r="A147">
-        <v>2044717717064</v>
+        <v>2044717717200</v>
       </c>
       <c r="B147">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148">
       <c r="A148">
-        <v>2044717717200</v>
+        <v>2044717717231</v>
       </c>
       <c r="B148">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
       <c r="A149">
-        <v>2044717717231</v>
+        <v>2044717717156</v>
       </c>
       <c r="B149">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150">
       <c r="A150">
-        <v>2044717717156</v>
+        <v>2044717717101</v>
       </c>
       <c r="B150">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
       <c r="A151">
-        <v>2044717717101</v>
+        <v>2044717717446</v>
       </c>
       <c r="B151">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="152">
       <c r="A152">
-        <v>2044717717446</v>
+        <v>2044717717118</v>
       </c>
       <c r="B152">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153">
       <c r="A153">
-        <v>2044717717118</v>
+        <v>2044717717248</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154">
-        <v>2044717717248</v>
+        <v>2044717717422</v>
       </c>
       <c r="B154">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155">
-        <v>2044717717422</v>
+        <v>2044717717170</v>
       </c>
       <c r="B155">
         <v>0</v>
@@ -1641,7 +1641,7 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>2044717717170</v>
+        <v>2044717717354</v>
       </c>
       <c r="B156">
         <v>0</v>
@@ -1649,23 +1649,23 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>2044717717354</v>
+        <v>2044717717460</v>
       </c>
       <c r="B157">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="158">
       <c r="A158">
-        <v>2044717717460</v>
+        <v>2044717717224</v>
       </c>
       <c r="B158">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
       <c r="A159">
-        <v>2044717717224</v>
+        <v>2044717717071</v>
       </c>
       <c r="B159">
         <v>0</v>
@@ -1673,7 +1673,7 @@
     </row>
     <row r="160">
       <c r="A160">
-        <v>2044717717071</v>
+        <v>2044717717088</v>
       </c>
       <c r="B160">
         <v>0</v>
@@ -1681,7 +1681,7 @@
     </row>
     <row r="161">
       <c r="A161">
-        <v>2044717717088</v>
+        <v>2044717717194</v>
       </c>
       <c r="B161">
         <v>0</v>
@@ -1689,39 +1689,39 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>2044717717194</v>
+        <v>2044717717378</v>
       </c>
       <c r="B162">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163">
       <c r="A163">
-        <v>2044717717378</v>
+        <v>2044717717095</v>
       </c>
       <c r="B163">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
       <c r="A164">
-        <v>2044717717095</v>
+        <v>2044717717484</v>
       </c>
       <c r="B164">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="165">
       <c r="A165">
-        <v>2044717717484</v>
+        <v>2044715906811</v>
       </c>
       <c r="B165">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
       <c r="A166">
-        <v>2044715906811</v>
+        <v>2044715906835</v>
       </c>
       <c r="B166">
         <v>0</v>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="167">
       <c r="A167">
-        <v>2044715906835</v>
+        <v>2044715906842</v>
       </c>
       <c r="B167">
         <v>0</v>
@@ -1737,23 +1737,23 @@
     </row>
     <row r="168">
       <c r="A168">
-        <v>2044715906842</v>
+        <v>2044715906859</v>
       </c>
       <c r="B168">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169">
       <c r="A169">
-        <v>2044715906859</v>
+        <v>2044715906866</v>
       </c>
       <c r="B169">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
       <c r="A170">
-        <v>2044715906866</v>
+        <v>2044715906873</v>
       </c>
       <c r="B170">
         <v>0</v>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>2044715906873</v>
+        <v>2044715906880</v>
       </c>
       <c r="B171">
         <v>0</v>
@@ -1769,23 +1769,23 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>2044715906880</v>
+        <v>2044715906897</v>
       </c>
       <c r="B172">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173">
       <c r="A173">
-        <v>2044715906897</v>
+        <v>2044715906903</v>
       </c>
       <c r="B173">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
       <c r="A174">
-        <v>2044715906903</v>
+        <v>2044715906910</v>
       </c>
       <c r="B174">
         <v>0</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="175">
       <c r="A175">
-        <v>2044715906910</v>
+        <v>2044715906927</v>
       </c>
       <c r="B175">
         <v>0</v>
@@ -1801,23 +1801,23 @@
     </row>
     <row r="176">
       <c r="A176">
-        <v>2044715906927</v>
+        <v>2044715906934</v>
       </c>
       <c r="B176">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177">
       <c r="A177">
-        <v>2044715906934</v>
+        <v>2044715906958</v>
       </c>
       <c r="B177">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="178">
       <c r="A178">
-        <v>2044715906958</v>
+        <v>2044715906965</v>
       </c>
       <c r="B178">
         <v>0</v>
@@ -1825,23 +1825,23 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>2044715906965</v>
+        <v>2044715906972</v>
       </c>
       <c r="B179">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180">
       <c r="A180">
-        <v>2044715906972</v>
+        <v>2044715906989</v>
       </c>
       <c r="B180">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="181">
       <c r="A181">
-        <v>2044715906989</v>
+        <v>2044715906996</v>
       </c>
       <c r="B181">
         <v>5</v>
@@ -1849,15 +1849,15 @@
     </row>
     <row r="182">
       <c r="A182">
-        <v>2044715906996</v>
+        <v>2044715907009</v>
       </c>
       <c r="B182">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="183">
       <c r="A183">
-        <v>2044715907009</v>
+        <v>2044715907023</v>
       </c>
       <c r="B183">
         <v>0</v>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="184">
       <c r="A184">
-        <v>2044715907023</v>
+        <v>2044715907030</v>
       </c>
       <c r="B184">
         <v>0</v>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="185">
       <c r="A185">
-        <v>2044715907030</v>
+        <v>2044715905807</v>
       </c>
       <c r="B185">
         <v>0</v>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>2044715905807</v>
+        <v>2044715905821</v>
       </c>
       <c r="B186">
         <v>0</v>
@@ -1889,7 +1889,7 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>2044715905821</v>
+        <v>2044715905838</v>
       </c>
       <c r="B187">
         <v>0</v>
@@ -1897,7 +1897,7 @@
     </row>
     <row r="188">
       <c r="A188">
-        <v>2044715905838</v>
+        <v>2044715905852</v>
       </c>
       <c r="B188">
         <v>0</v>
@@ -1905,23 +1905,23 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>2044715905852</v>
+        <v>2044715905869</v>
       </c>
       <c r="B189">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190">
       <c r="A190">
-        <v>2044715905869</v>
+        <v>2044715905876</v>
       </c>
       <c r="B190">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
       <c r="A191">
-        <v>2044715905876</v>
+        <v>2044715905883</v>
       </c>
       <c r="B191">
         <v>0</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="192">
       <c r="A192">
-        <v>2044715905883</v>
+        <v>2044715905906</v>
       </c>
       <c r="B192">
         <v>0</v>
@@ -1937,7 +1937,7 @@
     </row>
     <row r="193">
       <c r="A193">
-        <v>2044715905906</v>
+        <v>2044715905913</v>
       </c>
       <c r="B193">
         <v>0</v>
@@ -1945,7 +1945,7 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>2044715905913</v>
+        <v>2044715905920</v>
       </c>
       <c r="B194">
         <v>0</v>
@@ -1953,39 +1953,39 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>2044715905920</v>
+        <v>2044715905944</v>
       </c>
       <c r="B195">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="196">
       <c r="A196">
-        <v>2044715905944</v>
+        <v>2044715905951</v>
       </c>
       <c r="B196">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197">
       <c r="A197">
-        <v>2044715905951</v>
+        <v>2044715905968</v>
       </c>
       <c r="B197">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="198">
       <c r="A198">
-        <v>2044715905968</v>
+        <v>2044715905982</v>
       </c>
       <c r="B198">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="199">
       <c r="A199">
-        <v>2044715905982</v>
+        <v>2044715905999</v>
       </c>
       <c r="B199">
         <v>0</v>
@@ -1993,7 +1993,7 @@
     </row>
     <row r="200">
       <c r="A200">
-        <v>2044715905999</v>
+        <v>2044715906002</v>
       </c>
       <c r="B200">
         <v>0</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="201">
       <c r="A201">
-        <v>2044715906002</v>
+        <v>2044715906019</v>
       </c>
       <c r="B201">
         <v>0</v>
@@ -2009,7 +2009,7 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>2044715906019</v>
+        <v>2044715906026</v>
       </c>
       <c r="B202">
         <v>0</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="203">
       <c r="A203">
-        <v>2044715906026</v>
+        <v>2044715906040</v>
       </c>
       <c r="B203">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>2044715906040</v>
+        <v>2044715906057</v>
       </c>
       <c r="B204">
         <v>0</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="205">
       <c r="A205">
-        <v>2044715906057</v>
+        <v>2044715906071</v>
       </c>
       <c r="B205">
         <v>0</v>
@@ -2041,7 +2041,7 @@
     </row>
     <row r="206">
       <c r="A206">
-        <v>2044715906071</v>
+        <v>2044715906088</v>
       </c>
       <c r="B206">
         <v>0</v>
@@ -2049,7 +2049,7 @@
     </row>
     <row r="207">
       <c r="A207">
-        <v>2044715906088</v>
+        <v>2044715906095</v>
       </c>
       <c r="B207">
         <v>0</v>
@@ -2057,7 +2057,7 @@
     </row>
     <row r="208">
       <c r="A208">
-        <v>2044715906095</v>
+        <v>2044715906101</v>
       </c>
       <c r="B208">
         <v>0</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="209">
       <c r="A209">
-        <v>2044715906101</v>
+        <v>2044715906118</v>
       </c>
       <c r="B209">
         <v>0</v>
@@ -2073,7 +2073,7 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>2044715906118</v>
+        <v>2044715906125</v>
       </c>
       <c r="B210">
         <v>0</v>
@@ -2081,23 +2081,23 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>2044715906125</v>
+        <v>2044715906132</v>
       </c>
       <c r="B211">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="212">
       <c r="A212">
-        <v>2044715906132</v>
+        <v>2044715906545</v>
       </c>
       <c r="B212">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
       <c r="A213">
-        <v>2044715906545</v>
+        <v>2044715906552</v>
       </c>
       <c r="B213">
         <v>0</v>
@@ -2105,15 +2105,15 @@
     </row>
     <row r="214">
       <c r="A214">
-        <v>2044715906552</v>
+        <v>2044715906569</v>
       </c>
       <c r="B214">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="215">
       <c r="A215">
-        <v>2044715906569</v>
+        <v>2044715906576</v>
       </c>
       <c r="B215">
         <v>5</v>
@@ -2121,31 +2121,31 @@
     </row>
     <row r="216">
       <c r="A216">
-        <v>2044715906576</v>
+        <v>2044715906583</v>
       </c>
       <c r="B216">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
       <c r="A217">
-        <v>2044715906583</v>
+        <v>2044715906590</v>
       </c>
       <c r="B217">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="218">
       <c r="A218">
-        <v>2044715906590</v>
+        <v>2044715906606</v>
       </c>
       <c r="B218">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
       <c r="A219">
-        <v>2044715906606</v>
+        <v>2044715906613</v>
       </c>
       <c r="B219">
         <v>0</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>2044715906613</v>
+        <v>2044715906637</v>
       </c>
       <c r="B220">
         <v>0</v>
@@ -2161,23 +2161,23 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>2044715906637</v>
+        <v>2044715906644</v>
       </c>
       <c r="B221">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="222">
       <c r="A222">
-        <v>2044715906644</v>
+        <v>2044715906668</v>
       </c>
       <c r="B222">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="223">
       <c r="A223">
-        <v>2044715906668</v>
+        <v>2044715906675</v>
       </c>
       <c r="B223">
         <v>0</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="224">
       <c r="A224">
-        <v>2044715906675</v>
+        <v>2044715906682</v>
       </c>
       <c r="B224">
         <v>0</v>
@@ -2193,7 +2193,7 @@
     </row>
     <row r="225">
       <c r="A225">
-        <v>2044715906682</v>
+        <v>2044715906699</v>
       </c>
       <c r="B225">
         <v>0</v>
@@ -2201,23 +2201,23 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>2044715906699</v>
+        <v>2044715906705</v>
       </c>
       <c r="B226">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227">
       <c r="A227">
-        <v>2044715906705</v>
+        <v>2044715906729</v>
       </c>
       <c r="B227">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
       <c r="A228">
-        <v>2044715906729</v>
+        <v>2044715906736</v>
       </c>
       <c r="B228">
         <v>0</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>2044715906736</v>
+        <v>2044715906743</v>
       </c>
       <c r="B229">
         <v>0</v>
@@ -2233,7 +2233,7 @@
     </row>
     <row r="230">
       <c r="A230">
-        <v>2044715906743</v>
+        <v>2044715906767</v>
       </c>
       <c r="B230">
         <v>0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="231">
       <c r="A231">
-        <v>2044715906767</v>
+        <v>2044715906798</v>
       </c>
       <c r="B231">
         <v>0</v>
@@ -2249,15 +2249,15 @@
     </row>
     <row r="232">
       <c r="A232">
-        <v>2044715906798</v>
+        <v>2044719078644</v>
       </c>
       <c r="B232">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="233">
       <c r="A233">
-        <v>2044719078644</v>
+        <v>2044719078736</v>
       </c>
       <c r="B233">
         <v>5</v>
@@ -2265,7 +2265,7 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>2044719078736</v>
+        <v>2044719078040</v>
       </c>
       <c r="B234">
         <v>5</v>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>2044719078040</v>
+        <v>2044719078590</v>
       </c>
       <c r="B235">
         <v>5</v>
@@ -2281,15 +2281,15 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>2044719078590</v>
+        <v>2044719078514</v>
       </c>
       <c r="B236">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237">
       <c r="A237">
-        <v>2044719078514</v>
+        <v>2044719078842</v>
       </c>
       <c r="B237">
         <v>0</v>
@@ -2297,47 +2297,47 @@
     </row>
     <row r="238">
       <c r="A238">
-        <v>2044719078842</v>
+        <v>2044719079009</v>
       </c>
       <c r="B238">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="239">
       <c r="A239">
-        <v>2044719079009</v>
+        <v>2044719078217</v>
       </c>
       <c r="B239">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240">
-        <v>2044719078217</v>
+        <v>2044719078804</v>
       </c>
       <c r="B240">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241">
       <c r="A241">
-        <v>2044719078804</v>
+        <v>2044719079047</v>
       </c>
       <c r="B241">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242">
-        <v>2044719079047</v>
+        <v>2044719078460</v>
       </c>
       <c r="B242">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="243">
       <c r="A243">
-        <v>2044719078460</v>
+        <v>2044719078125</v>
       </c>
       <c r="B243">
         <v>5</v>
@@ -2345,15 +2345,15 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>2044719078125</v>
+        <v>2044719078170</v>
       </c>
       <c r="B244">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
       <c r="A245">
-        <v>2044719078170</v>
+        <v>2044719078477</v>
       </c>
       <c r="B245">
         <v>0</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="246">
       <c r="A246">
-        <v>2044719078477</v>
+        <v>2044719078507</v>
       </c>
       <c r="B246">
         <v>0</v>
@@ -2369,31 +2369,31 @@
     </row>
     <row r="247">
       <c r="A247">
-        <v>2044719078507</v>
+        <v>2044719078705</v>
       </c>
       <c r="B247">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248">
       <c r="A248">
-        <v>2044719078705</v>
+        <v>2044719079023</v>
       </c>
       <c r="B248">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
       <c r="A249">
-        <v>2044719079023</v>
+        <v>2044719078835</v>
       </c>
       <c r="B249">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="250">
       <c r="A250">
-        <v>2044719078835</v>
+        <v>2044719078484</v>
       </c>
       <c r="B250">
         <v>5</v>
@@ -2401,31 +2401,31 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>2044719078484</v>
+        <v>2044719078965</v>
       </c>
       <c r="B251">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="252">
       <c r="A252">
-        <v>2044719078965</v>
+        <v>2044719079016</v>
       </c>
       <c r="B252">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="253">
       <c r="A253">
-        <v>2044719079016</v>
+        <v>2044719078255</v>
       </c>
       <c r="B253">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
       <c r="A254">
-        <v>2044719078255</v>
+        <v>2044719078668</v>
       </c>
       <c r="B254">
         <v>0</v>
@@ -2433,7 +2433,7 @@
     </row>
     <row r="255">
       <c r="A255">
-        <v>2044719078668</v>
+        <v>2044719078088</v>
       </c>
       <c r="B255">
         <v>0</v>
@@ -2441,7 +2441,7 @@
     </row>
     <row r="256">
       <c r="A256">
-        <v>2044719078088</v>
+        <v>2044719078491</v>
       </c>
       <c r="B256">
         <v>0</v>
@@ -2449,15 +2449,15 @@
     </row>
     <row r="257">
       <c r="A257">
-        <v>2044719078491</v>
+        <v>2044719078651</v>
       </c>
       <c r="B257">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="258">
       <c r="A258">
-        <v>2044719078651</v>
+        <v>2044719078620</v>
       </c>
       <c r="B258">
         <v>5</v>
@@ -2465,15 +2465,15 @@
     </row>
     <row r="259">
       <c r="A259">
-        <v>2044719078620</v>
+        <v>2044719078712</v>
       </c>
       <c r="B259">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
       <c r="A260">
-        <v>2044719078712</v>
+        <v>2044719079030</v>
       </c>
       <c r="B260">
         <v>0</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>2044719079030</v>
+        <v>2044719078200</v>
       </c>
       <c r="B261">
         <v>0</v>
@@ -2489,15 +2489,15 @@
     </row>
     <row r="262">
       <c r="A262">
-        <v>2044719078200</v>
+        <v>2044719078828</v>
       </c>
       <c r="B262">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="263">
       <c r="A263">
-        <v>2044719078828</v>
+        <v>2044719078538</v>
       </c>
       <c r="B263">
         <v>5</v>
@@ -2505,15 +2505,15 @@
     </row>
     <row r="264">
       <c r="A264">
-        <v>2044719078538</v>
+        <v>2044719078972</v>
       </c>
       <c r="B264">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265">
       <c r="A265">
-        <v>2044719078972</v>
+        <v>2044719078866</v>
       </c>
       <c r="B265">
         <v>0</v>
@@ -2521,23 +2521,23 @@
     </row>
     <row r="266">
       <c r="A266">
-        <v>2044719078866</v>
+        <v>2044719078613</v>
       </c>
       <c r="B266">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267">
       <c r="A267">
-        <v>2044719078613</v>
+        <v>2044719078071</v>
       </c>
       <c r="B267">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268">
       <c r="A268">
-        <v>2044719078071</v>
+        <v>2044719078132</v>
       </c>
       <c r="B268">
         <v>0</v>
@@ -2545,15 +2545,15 @@
     </row>
     <row r="269">
       <c r="A269">
-        <v>2044719078132</v>
+        <v>2044719078446</v>
       </c>
       <c r="B269">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="270">
       <c r="A270">
-        <v>2044719078446</v>
+        <v>2044719078163</v>
       </c>
       <c r="B270">
         <v>5</v>
@@ -2561,7 +2561,7 @@
     </row>
     <row r="271">
       <c r="A271">
-        <v>2044719078163</v>
+        <v>2044719078873</v>
       </c>
       <c r="B271">
         <v>5</v>
@@ -2569,15 +2569,15 @@
     </row>
     <row r="272">
       <c r="A272">
-        <v>2044719078873</v>
+        <v>2044719078729</v>
       </c>
       <c r="B272">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
       <c r="A273">
-        <v>2044719078729</v>
+        <v>2044719078743</v>
       </c>
       <c r="B273">
         <v>0</v>
@@ -2585,23 +2585,23 @@
     </row>
     <row r="274">
       <c r="A274">
-        <v>2044719078743</v>
+        <v>2044719078569</v>
       </c>
       <c r="B274">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="275">
       <c r="A275">
-        <v>2044719078569</v>
+        <v>2044719078248</v>
       </c>
       <c r="B275">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276">
-        <v>2044719078248</v>
+        <v>2044719078903</v>
       </c>
       <c r="B276">
         <v>0</v>
@@ -2609,15 +2609,15 @@
     </row>
     <row r="277">
       <c r="A277">
-        <v>2044719078903</v>
+        <v>2044719078156</v>
       </c>
       <c r="B277">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278">
       <c r="A278">
-        <v>2044719078156</v>
+        <v>2044719078781</v>
       </c>
       <c r="B278">
         <v>5</v>
@@ -2625,7 +2625,7 @@
     </row>
     <row r="279">
       <c r="A279">
-        <v>2044719078781</v>
+        <v>2044719078996</v>
       </c>
       <c r="B279">
         <v>5</v>
@@ -2633,7 +2633,7 @@
     </row>
     <row r="280">
       <c r="A280">
-        <v>2044719078996</v>
+        <v>2044719078699</v>
       </c>
       <c r="B280">
         <v>5</v>
@@ -2641,7 +2641,7 @@
     </row>
     <row r="281">
       <c r="A281">
-        <v>2044719078699</v>
+        <v>2044719078439</v>
       </c>
       <c r="B281">
         <v>5</v>
@@ -2649,7 +2649,7 @@
     </row>
     <row r="282">
       <c r="A282">
-        <v>2044719078439</v>
+        <v>2044719078583</v>
       </c>
       <c r="B282">
         <v>5</v>
@@ -2657,15 +2657,15 @@
     </row>
     <row r="283">
       <c r="A283">
-        <v>2044719078583</v>
+        <v>2044719078545</v>
       </c>
       <c r="B283">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
       <c r="A284">
-        <v>2044719078545</v>
+        <v>2044719078989</v>
       </c>
       <c r="B284">
         <v>0</v>
@@ -2673,15 +2673,15 @@
     </row>
     <row r="285">
       <c r="A285">
-        <v>2044719078989</v>
+        <v>2044719078231</v>
       </c>
       <c r="B285">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286">
       <c r="A286">
-        <v>2044719078231</v>
+        <v>2044719078941</v>
       </c>
       <c r="B286">
         <v>5</v>
@@ -2689,7 +2689,7 @@
     </row>
     <row r="287">
       <c r="A287">
-        <v>2044719078941</v>
+        <v>2044719078453</v>
       </c>
       <c r="B287">
         <v>5</v>
@@ -2697,7 +2697,7 @@
     </row>
     <row r="288">
       <c r="A288">
-        <v>2044719078453</v>
+        <v>2044719078897</v>
       </c>
       <c r="B288">
         <v>5</v>
@@ -2705,15 +2705,15 @@
     </row>
     <row r="289">
       <c r="A289">
-        <v>2044719078897</v>
+        <v>2044719078118</v>
       </c>
       <c r="B289">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290">
-        <v>2044719078118</v>
+        <v>2044719078576</v>
       </c>
       <c r="B290">
         <v>0</v>
@@ -2721,23 +2721,23 @@
     </row>
     <row r="291">
       <c r="A291">
-        <v>2044719078576</v>
+        <v>2044719078194</v>
       </c>
       <c r="B291">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="292">
       <c r="A292">
-        <v>2044719078194</v>
+        <v>2044719078774</v>
       </c>
       <c r="B292">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c r="A293">
-        <v>2044719078774</v>
+        <v>2044719078149</v>
       </c>
       <c r="B293">
         <v>0</v>
@@ -2745,31 +2745,31 @@
     </row>
     <row r="294">
       <c r="A294">
-        <v>2044719078149</v>
+        <v>2044719078187</v>
       </c>
       <c r="B294">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="295">
       <c r="A295">
-        <v>2044719078187</v>
+        <v>2044719078859</v>
       </c>
       <c r="B295">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296">
-        <v>2044719078859</v>
+        <v>2044719078064</v>
       </c>
       <c r="B296">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297">
-        <v>2044719078064</v>
+        <v>2044719078750</v>
       </c>
       <c r="B297">
         <v>0</v>
@@ -2777,7 +2777,7 @@
     </row>
     <row r="298">
       <c r="A298">
-        <v>2044719078750</v>
+        <v>2044719078880</v>
       </c>
       <c r="B298">
         <v>0</v>
@@ -2785,31 +2785,31 @@
     </row>
     <row r="299">
       <c r="A299">
-        <v>2044719078880</v>
+        <v>2044719078057</v>
       </c>
       <c r="B299">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="300">
       <c r="A300">
-        <v>2044719078057</v>
+        <v>2044719078224</v>
       </c>
       <c r="B300">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301">
-        <v>2044719078224</v>
+        <v>2044661682678</v>
       </c>
       <c r="B301">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="302">
       <c r="A302">
-        <v>2044661682678</v>
+        <v>2044661682753</v>
       </c>
       <c r="B302">
         <v>5</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="303">
       <c r="A303">
-        <v>2044661682753</v>
+        <v>2044661682715</v>
       </c>
       <c r="B303">
         <v>5</v>
@@ -2825,23 +2825,23 @@
     </row>
     <row r="304">
       <c r="A304">
-        <v>2044661682715</v>
+        <v>2044661682814</v>
       </c>
       <c r="B304">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305">
-        <v>2044661682814</v>
+        <v>2044661682425</v>
       </c>
       <c r="B305">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="306">
       <c r="A306">
-        <v>2044661682425</v>
+        <v>2044661682654</v>
       </c>
       <c r="B306">
         <v>5</v>
@@ -2849,23 +2849,23 @@
     </row>
     <row r="307">
       <c r="A307">
-        <v>2044661682654</v>
+        <v>2044661682708</v>
       </c>
       <c r="B307">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="308">
       <c r="A308">
-        <v>2044661682708</v>
+        <v>2044661682548</v>
       </c>
       <c r="B308">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309">
       <c r="A309">
-        <v>2044661682548</v>
+        <v>2044661682487</v>
       </c>
       <c r="B309">
         <v>5</v>
@@ -2873,15 +2873,15 @@
     </row>
     <row r="310">
       <c r="A310">
-        <v>2044661682487</v>
+        <v>2044661682456</v>
       </c>
       <c r="B310">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
       <c r="A311">
-        <v>2044661682456</v>
+        <v>2044661682784</v>
       </c>
       <c r="B311">
         <v>0</v>
@@ -2889,7 +2889,7 @@
     </row>
     <row r="312">
       <c r="A312">
-        <v>2044661682784</v>
+        <v>2044661682463</v>
       </c>
       <c r="B312">
         <v>0</v>
@@ -2897,23 +2897,23 @@
     </row>
     <row r="313">
       <c r="A313">
-        <v>2044661682463</v>
+        <v>2044661682524</v>
       </c>
       <c r="B313">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314">
       <c r="A314">
-        <v>2044661682524</v>
+        <v>2044661682623</v>
       </c>
       <c r="B314">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315">
       <c r="A315">
-        <v>2044661682623</v>
+        <v>2044661682777</v>
       </c>
       <c r="B315">
         <v>0</v>
@@ -2921,7 +2921,7 @@
     </row>
     <row r="316">
       <c r="A316">
-        <v>2044661682777</v>
+        <v>2044661682593</v>
       </c>
       <c r="B316">
         <v>0</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="317">
       <c r="A317">
-        <v>2044661682593</v>
+        <v>2044661682449</v>
       </c>
       <c r="B317">
         <v>0</v>
@@ -2937,7 +2937,7 @@
     </row>
     <row r="318">
       <c r="A318">
-        <v>2044661682449</v>
+        <v>2044661682500</v>
       </c>
       <c r="B318">
         <v>0</v>
@@ -2945,23 +2945,23 @@
     </row>
     <row r="319">
       <c r="A319">
-        <v>2044661682500</v>
+        <v>2044661682739</v>
       </c>
       <c r="B319">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="320">
       <c r="A320">
-        <v>2044661682739</v>
+        <v>2044661682685</v>
       </c>
       <c r="B320">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321">
-        <v>2044661682685</v>
+        <v>2044661682616</v>
       </c>
       <c r="B321">
         <v>0</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="322">
       <c r="A322">
-        <v>2044661682616</v>
+        <v>2044661682791</v>
       </c>
       <c r="B322">
         <v>0</v>
@@ -2977,7 +2977,7 @@
     </row>
     <row r="323">
       <c r="A323">
-        <v>2044661682791</v>
+        <v>2044661682586</v>
       </c>
       <c r="B323">
         <v>0</v>
@@ -2985,15 +2985,15 @@
     </row>
     <row r="324">
       <c r="A324">
-        <v>2044661682586</v>
+        <v>2044661682562</v>
       </c>
       <c r="B324">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325">
-      <c r="A325">
-        <v>2044661682562</v>
+      <c r="A325" t="str">
+        <v>2046921819367</v>
       </c>
       <c r="B325">
         <v>5</v>
@@ -3001,7 +3001,7 @@
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>2046921819367</v>
+        <v>2046921819299</v>
       </c>
       <c r="B326">
         <v>5</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>2046921819299</v>
+        <v>2046921819282</v>
       </c>
       <c r="B327">
         <v>5</v>
@@ -3017,23 +3017,23 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>2046921819282</v>
+        <v>2046921819626</v>
       </c>
       <c r="B328">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>2046921819626</v>
+        <v>2046921819565</v>
       </c>
       <c r="B329">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>2046921819565</v>
+        <v>2046921819510</v>
       </c>
       <c r="B330">
         <v>5</v>
@@ -3041,23 +3041,23 @@
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>2046921819510</v>
+        <v>2046921819343</v>
       </c>
       <c r="B331">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>2046921819343</v>
+        <v>2046921819329</v>
       </c>
       <c r="B332">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>2046921819329</v>
+        <v>2046921819558</v>
       </c>
       <c r="B333">
         <v>5</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>2046921819558</v>
+        <v>2046921819527</v>
       </c>
       <c r="B334">
         <v>5</v>
@@ -3073,7 +3073,7 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>2046921819527</v>
+        <v>2046921819480</v>
       </c>
       <c r="B335">
         <v>5</v>
@@ -3081,7 +3081,7 @@
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>2046921819480</v>
+        <v>2046921819411</v>
       </c>
       <c r="B336">
         <v>5</v>
@@ -3089,7 +3089,7 @@
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>2046921819411</v>
+        <v>2046921819435</v>
       </c>
       <c r="B337">
         <v>5</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>2046921819435</v>
+        <v>2046920701731</v>
       </c>
       <c r="B338">
         <v>5</v>
@@ -3105,7 +3105,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>2046920701731</v>
+        <v>2046921819657</v>
       </c>
       <c r="B339">
         <v>5</v>
@@ -3113,7 +3113,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>2046921819657</v>
+        <v>2046921819596</v>
       </c>
       <c r="B340">
         <v>5</v>
@@ -3121,23 +3121,23 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>2046921819596</v>
+        <v>2046921819404</v>
       </c>
       <c r="B341">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>2046921819404</v>
+        <v>2046921671828</v>
       </c>
       <c r="B342">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>2046921671828</v>
+        <v>2046921819466</v>
       </c>
       <c r="B343">
         <v>5</v>
@@ -3145,7 +3145,7 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>2046921819466</v>
+        <v>2046921819305</v>
       </c>
       <c r="B344">
         <v>5</v>
@@ -3153,15 +3153,15 @@
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>2046921819305</v>
+        <v>2046921819541</v>
       </c>
       <c r="B345">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>2046921819541</v>
+        <v>2046921819503</v>
       </c>
       <c r="B346">
         <v>0</v>
@@ -3169,7 +3169,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>2046921819503</v>
+        <v>2046921819398</v>
       </c>
       <c r="B347">
         <v>0</v>
@@ -3177,15 +3177,15 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>2046921819398</v>
+        <v>2046921819350</v>
       </c>
       <c r="B348">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>2046921819350</v>
+        <v>2046921819381</v>
       </c>
       <c r="B349">
         <v>5</v>
@@ -3193,7 +3193,7 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>2046921819381</v>
+        <v>2046921819312</v>
       </c>
       <c r="B350">
         <v>5</v>
@@ -3201,39 +3201,39 @@
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>2046921819312</v>
+        <v>2046921819336</v>
       </c>
       <c r="B351">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>2046921819336</v>
+        <v>2046921819473</v>
       </c>
       <c r="B352">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353">
-      <c r="A353" t="str">
-        <v>2046921819473</v>
+      <c r="A353">
+        <v>2047878479765</v>
       </c>
       <c r="B353">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
       <c r="A354">
-        <v>2047878479765</v>
+        <v>2047878479789</v>
       </c>
       <c r="B354">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355">
       <c r="A355">
-        <v>2047878479789</v>
+        <v>2047878479796</v>
       </c>
       <c r="B355">
         <v>5</v>
@@ -3241,15 +3241,15 @@
     </row>
     <row r="356">
       <c r="A356">
-        <v>2047878479796</v>
+        <v>2047878479802</v>
       </c>
       <c r="B356">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="357">
       <c r="A357">
-        <v>2047878479802</v>
+        <v>2047878479826</v>
       </c>
       <c r="B357">
         <v>0</v>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="358">
       <c r="A358">
-        <v>2047878479826</v>
+        <v>2047878479840</v>
       </c>
       <c r="B358">
         <v>0</v>
@@ -3265,7 +3265,7 @@
     </row>
     <row r="359">
       <c r="A359">
-        <v>2047878479840</v>
+        <v>2047878479857</v>
       </c>
       <c r="B359">
         <v>0</v>
@@ -3273,15 +3273,15 @@
     </row>
     <row r="360">
       <c r="A360">
-        <v>2047878479857</v>
+        <v>2047878479864</v>
       </c>
       <c r="B360">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
       <c r="A361">
-        <v>2047878479864</v>
+        <v>2047878479871</v>
       </c>
       <c r="B361">
         <v>0</v>
@@ -3289,7 +3289,7 @@
     </row>
     <row r="362">
       <c r="A362">
-        <v>2047878479871</v>
+        <v>2047878479888</v>
       </c>
       <c r="B362">
         <v>0</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="363">
       <c r="A363">
-        <v>2047878479888</v>
+        <v>2047878479895</v>
       </c>
       <c r="B363">
         <v>0</v>
@@ -3305,7 +3305,7 @@
     </row>
     <row r="364">
       <c r="A364">
-        <v>2047878479895</v>
+        <v>2047878479918</v>
       </c>
       <c r="B364">
         <v>0</v>
@@ -3313,7 +3313,7 @@
     </row>
     <row r="365">
       <c r="A365">
-        <v>2047878479918</v>
+        <v>2047878479932</v>
       </c>
       <c r="B365">
         <v>0</v>
@@ -3321,7 +3321,7 @@
     </row>
     <row r="366">
       <c r="A366">
-        <v>2047878479932</v>
+        <v>2047878479949</v>
       </c>
       <c r="B366">
         <v>0</v>
@@ -3329,7 +3329,7 @@
     </row>
     <row r="367">
       <c r="A367">
-        <v>2047878479949</v>
+        <v>2047878479956</v>
       </c>
       <c r="B367">
         <v>0</v>
@@ -3337,7 +3337,7 @@
     </row>
     <row r="368">
       <c r="A368">
-        <v>2047878479956</v>
+        <v>2047878479963</v>
       </c>
       <c r="B368">
         <v>0</v>
@@ -3345,15 +3345,15 @@
     </row>
     <row r="369">
       <c r="A369">
-        <v>2047878479963</v>
+        <v>2047878479970</v>
       </c>
       <c r="B369">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
       <c r="A370">
-        <v>2047878479970</v>
+        <v>2047878479994</v>
       </c>
       <c r="B370">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     </row>
     <row r="371">
       <c r="A371">
-        <v>2047878479994</v>
+        <v>2047878480006</v>
       </c>
       <c r="B371">
         <v>0</v>
@@ -3369,7 +3369,7 @@
     </row>
     <row r="372">
       <c r="A372">
-        <v>2047878480006</v>
+        <v>2047878480013</v>
       </c>
       <c r="B372">
         <v>0</v>
@@ -3377,71 +3377,71 @@
     </row>
     <row r="373">
       <c r="A373">
-        <v>2047878480013</v>
+        <v>2047878480037</v>
       </c>
       <c r="B373">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="374">
       <c r="A374">
-        <v>2047878480037</v>
+        <v>2047878480044</v>
       </c>
       <c r="B374">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
       <c r="A375">
-        <v>2047878480044</v>
+        <v>2047878480051</v>
       </c>
       <c r="B375">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="376">
       <c r="A376">
-        <v>2047878480051</v>
+        <v>2047878480099</v>
       </c>
       <c r="B376">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
       <c r="A377">
-        <v>2047878480099</v>
+        <v>2047878480143</v>
       </c>
       <c r="B377">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="378">
       <c r="A378">
-        <v>2047878480143</v>
+        <v>2047878480204</v>
       </c>
       <c r="B378">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
       <c r="A379">
-        <v>2047878480204</v>
+        <v>2047878480228</v>
       </c>
       <c r="B379">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380">
       <c r="A380">
-        <v>2047878480228</v>
+        <v>2047878477891</v>
       </c>
       <c r="B380">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
       <c r="A381">
-        <v>2047878477891</v>
+        <v>2047878477921</v>
       </c>
       <c r="B381">
         <v>0</v>
@@ -3449,23 +3449,23 @@
     </row>
     <row r="382">
       <c r="A382">
-        <v>2047878477921</v>
+        <v>2047878477952</v>
       </c>
       <c r="B382">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="383">
       <c r="A383">
-        <v>2047878477952</v>
+        <v>2047878477976</v>
       </c>
       <c r="B383">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="384">
       <c r="A384">
-        <v>2047878477976</v>
+        <v>2047878477990</v>
       </c>
       <c r="B384">
         <v>0</v>
@@ -3473,15 +3473,15 @@
     </row>
     <row r="385">
       <c r="A385">
-        <v>2047878477990</v>
+        <v>2047878478027</v>
       </c>
       <c r="B385">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386">
       <c r="A386">
-        <v>2047878478027</v>
+        <v>2047878478034</v>
       </c>
       <c r="B386">
         <v>5</v>
@@ -3489,7 +3489,7 @@
     </row>
     <row r="387">
       <c r="A387">
-        <v>2047878478034</v>
+        <v>2047878478058</v>
       </c>
       <c r="B387">
         <v>5</v>
@@ -3497,7 +3497,7 @@
     </row>
     <row r="388">
       <c r="A388">
-        <v>2047878478058</v>
+        <v>2047878478089</v>
       </c>
       <c r="B388">
         <v>5</v>
@@ -3505,15 +3505,15 @@
     </row>
     <row r="389">
       <c r="A389">
-        <v>2047878478089</v>
+        <v>2047878478102</v>
       </c>
       <c r="B389">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
       <c r="A390">
-        <v>2047878478102</v>
+        <v>2047878478133</v>
       </c>
       <c r="B390">
         <v>0</v>
@@ -3521,23 +3521,23 @@
     </row>
     <row r="391">
       <c r="A391">
-        <v>2047878478133</v>
+        <v>2047878478140</v>
       </c>
       <c r="B391">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="392">
       <c r="A392">
-        <v>2047878478140</v>
+        <v>2047878478157</v>
       </c>
       <c r="B392">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="393">
       <c r="A393">
-        <v>2047878478157</v>
+        <v>2047878478171</v>
       </c>
       <c r="B393">
         <v>0</v>
@@ -3545,7 +3545,7 @@
     </row>
     <row r="394">
       <c r="A394">
-        <v>2047878478171</v>
+        <v>2047878478195</v>
       </c>
       <c r="B394">
         <v>0</v>
@@ -3553,15 +3553,15 @@
     </row>
     <row r="395">
       <c r="A395">
-        <v>2047878478195</v>
+        <v>2047878478218</v>
       </c>
       <c r="B395">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="396">
       <c r="A396">
-        <v>2047878478218</v>
+        <v>2047878478225</v>
       </c>
       <c r="B396">
         <v>5</v>
@@ -3569,55 +3569,55 @@
     </row>
     <row r="397">
       <c r="A397">
-        <v>2047878478225</v>
+        <v>2047878478232</v>
       </c>
       <c r="B397">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
       <c r="A398">
-        <v>2047878478232</v>
+        <v>2047878478256</v>
       </c>
       <c r="B398">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399">
       <c r="A399">
-        <v>2047878478256</v>
+        <v>2047878478270</v>
       </c>
       <c r="B399">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
       <c r="A400">
-        <v>2047878478270</v>
+        <v>2047878478287</v>
       </c>
       <c r="B400">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="401">
       <c r="A401">
-        <v>2047878478287</v>
+        <v>2047879518708</v>
       </c>
       <c r="B401">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="402">
       <c r="A402">
-        <v>2047879518708</v>
+        <v>2047879518715</v>
       </c>
       <c r="B402">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403">
       <c r="A403">
-        <v>2047879518715</v>
+        <v>2047879518722</v>
       </c>
       <c r="B403">
         <v>5</v>
@@ -3625,7 +3625,7 @@
     </row>
     <row r="404">
       <c r="A404">
-        <v>2047879518722</v>
+        <v>2048174920791</v>
       </c>
       <c r="B404">
         <v>5</v>
@@ -3633,7 +3633,7 @@
     </row>
     <row r="405">
       <c r="A405">
-        <v>2048174920791</v>
+        <v>2048174920807</v>
       </c>
       <c r="B405">
         <v>5</v>
@@ -3641,15 +3641,15 @@
     </row>
     <row r="406">
       <c r="A406">
-        <v>2048174920807</v>
+        <v>2048174920814</v>
       </c>
       <c r="B406">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
       <c r="A407">
-        <v>2048174920814</v>
+        <v>2047878478317</v>
       </c>
       <c r="B407">
         <v>0</v>
@@ -3657,15 +3657,15 @@
     </row>
     <row r="408">
       <c r="A408">
-        <v>2047878478317</v>
+        <v>2047878478324</v>
       </c>
       <c r="B408">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="409">
       <c r="A409">
-        <v>2047878478324</v>
+        <v>2047878478447</v>
       </c>
       <c r="B409">
         <v>5</v>
@@ -3673,7 +3673,7 @@
     </row>
     <row r="410">
       <c r="A410">
-        <v>2047878478447</v>
+        <v>2047878478454</v>
       </c>
       <c r="B410">
         <v>5</v>
@@ -3681,15 +3681,15 @@
     </row>
     <row r="411">
       <c r="A411">
-        <v>2047878478454</v>
+        <v>2047878478478</v>
       </c>
       <c r="B411">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="412">
       <c r="A412">
-        <v>2047878478478</v>
+        <v>2047878478492</v>
       </c>
       <c r="B412">
         <v>0</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="413">
       <c r="A413">
-        <v>2047878478492</v>
+        <v>2047878478522</v>
       </c>
       <c r="B413">
         <v>5</v>
@@ -3705,15 +3705,15 @@
     </row>
     <row r="414">
       <c r="A414">
-        <v>2047878478522</v>
+        <v>2047878478553</v>
       </c>
       <c r="B414">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415">
-        <v>2047878478553</v>
+        <v>2047878478621</v>
       </c>
       <c r="B415">
         <v>0</v>
@@ -3721,7 +3721,7 @@
     </row>
     <row r="416">
       <c r="A416">
-        <v>2047878478621</v>
+        <v>2047878478645</v>
       </c>
       <c r="B416">
         <v>0</v>
@@ -3729,23 +3729,23 @@
     </row>
     <row r="417">
       <c r="A417">
-        <v>2047878478645</v>
+        <v>2047878478683</v>
       </c>
       <c r="B417">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="418">
       <c r="A418">
-        <v>2047878478683</v>
+        <v>2047878478737</v>
       </c>
       <c r="B418">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
       <c r="A419">
-        <v>2047878478737</v>
+        <v>2047878478768</v>
       </c>
       <c r="B419">
         <v>0</v>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="420">
       <c r="A420">
-        <v>2047878478768</v>
+        <v>2047878478812</v>
       </c>
       <c r="B420">
         <v>0</v>
@@ -3761,7 +3761,7 @@
     </row>
     <row r="421">
       <c r="A421">
-        <v>2047878478812</v>
+        <v>2047878478850</v>
       </c>
       <c r="B421">
         <v>0</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="422">
       <c r="A422">
-        <v>2047878478850</v>
+        <v>2047878478874</v>
       </c>
       <c r="B422">
         <v>0</v>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="423">
       <c r="A423">
-        <v>2047878478874</v>
+        <v>2047878478904</v>
       </c>
       <c r="B423">
         <v>0</v>
@@ -3785,7 +3785,7 @@
     </row>
     <row r="424">
       <c r="A424">
-        <v>2047878478904</v>
+        <v>2047878478911</v>
       </c>
       <c r="B424">
         <v>0</v>
@@ -3793,7 +3793,7 @@
     </row>
     <row r="425">
       <c r="A425">
-        <v>2047878478911</v>
+        <v>2047878478928</v>
       </c>
       <c r="B425">
         <v>0</v>
@@ -3801,7 +3801,7 @@
     </row>
     <row r="426">
       <c r="A426">
-        <v>2047878478928</v>
+        <v>2047878478935</v>
       </c>
       <c r="B426">
         <v>0</v>
@@ -3809,7 +3809,7 @@
     </row>
     <row r="427">
       <c r="A427">
-        <v>2047878478935</v>
+        <v>2047878478973</v>
       </c>
       <c r="B427">
         <v>0</v>
@@ -3817,7 +3817,7 @@
     </row>
     <row r="428">
       <c r="A428">
-        <v>2047878478973</v>
+        <v>2047878478997</v>
       </c>
       <c r="B428">
         <v>0</v>
@@ -3825,7 +3825,7 @@
     </row>
     <row r="429">
       <c r="A429">
-        <v>2047878478997</v>
+        <v>2047878479017</v>
       </c>
       <c r="B429">
         <v>5</v>
@@ -3833,15 +3833,15 @@
     </row>
     <row r="430">
       <c r="A430">
-        <v>2047878479017</v>
+        <v>2047878479031</v>
       </c>
       <c r="B430">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
       <c r="A431">
-        <v>2047878479031</v>
+        <v>2047878479055</v>
       </c>
       <c r="B431">
         <v>0</v>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="432">
       <c r="A432">
-        <v>2047878479055</v>
+        <v>2047878479079</v>
       </c>
       <c r="B432">
         <v>0</v>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="433">
       <c r="A433">
-        <v>2047878479079</v>
+        <v>2047878479086</v>
       </c>
       <c r="B433">
         <v>0</v>
@@ -3865,7 +3865,7 @@
     </row>
     <row r="434">
       <c r="A434">
-        <v>2047878479086</v>
+        <v>2047878479123</v>
       </c>
       <c r="B434">
         <v>0</v>
@@ -3873,7 +3873,7 @@
     </row>
     <row r="435">
       <c r="A435">
-        <v>2047878479123</v>
+        <v>2047878479154</v>
       </c>
       <c r="B435">
         <v>0</v>
@@ -3881,15 +3881,15 @@
     </row>
     <row r="436">
       <c r="A436">
-        <v>2047878479154</v>
+        <v>2047878479178</v>
       </c>
       <c r="B436">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
       <c r="A437">
-        <v>2047878479178</v>
+        <v>2047878479208</v>
       </c>
       <c r="B437">
         <v>0</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="438">
       <c r="A438">
-        <v>2047878479208</v>
+        <v>2047878479215</v>
       </c>
       <c r="B438">
         <v>0</v>
@@ -3905,23 +3905,23 @@
     </row>
     <row r="439">
       <c r="A439">
-        <v>2047878479215</v>
+        <v>2047878479253</v>
       </c>
       <c r="B439">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="440">
       <c r="A440">
-        <v>2047878479253</v>
+        <v>2047878479260</v>
       </c>
       <c r="B440">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
       <c r="A441">
-        <v>2047878479260</v>
+        <v>2047878479284</v>
       </c>
       <c r="B441">
         <v>0</v>
@@ -3929,7 +3929,7 @@
     </row>
     <row r="442">
       <c r="A442">
-        <v>2047878479284</v>
+        <v>2047878479307</v>
       </c>
       <c r="B442">
         <v>0</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="443">
       <c r="A443">
-        <v>2047878479307</v>
+        <v>2047878479338</v>
       </c>
       <c r="B443">
         <v>0</v>
@@ -3945,7 +3945,7 @@
     </row>
     <row r="444">
       <c r="A444">
-        <v>2047878479338</v>
+        <v>2047878479369</v>
       </c>
       <c r="B444">
         <v>0</v>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="445">
       <c r="A445">
-        <v>2047878479369</v>
+        <v>2047878479413</v>
       </c>
       <c r="B445">
         <v>0</v>
@@ -3961,7 +3961,7 @@
     </row>
     <row r="446">
       <c r="A446">
-        <v>2047878479413</v>
+        <v>2047878479437</v>
       </c>
       <c r="B446">
         <v>0</v>
@@ -3969,7 +3969,7 @@
     </row>
     <row r="447">
       <c r="A447">
-        <v>2047878479437</v>
+        <v>2047878479451</v>
       </c>
       <c r="B447">
         <v>0</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="448">
       <c r="A448">
-        <v>2047878479451</v>
+        <v>2047878479468</v>
       </c>
       <c r="B448">
         <v>0</v>
@@ -3985,7 +3985,7 @@
     </row>
     <row r="449">
       <c r="A449">
-        <v>2047878479468</v>
+        <v>2047878479482</v>
       </c>
       <c r="B449">
         <v>0</v>
@@ -3993,7 +3993,7 @@
     </row>
     <row r="450">
       <c r="A450">
-        <v>2047878479482</v>
+        <v>2047878479505</v>
       </c>
       <c r="B450">
         <v>0</v>
@@ -4001,15 +4001,15 @@
     </row>
     <row r="451">
       <c r="A451">
-        <v>2047878479505</v>
+        <v>2047878479536</v>
       </c>
       <c r="B451">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452">
       <c r="A452">
-        <v>2047878479536</v>
+        <v>2047878479574</v>
       </c>
       <c r="B452">
         <v>5</v>
@@ -4017,15 +4017,15 @@
     </row>
     <row r="453">
       <c r="A453">
-        <v>2047878479574</v>
+        <v>2047878479581</v>
       </c>
       <c r="B453">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
       <c r="A454">
-        <v>2047878479581</v>
+        <v>2047878479611</v>
       </c>
       <c r="B454">
         <v>0</v>
@@ -4033,39 +4033,39 @@
     </row>
     <row r="455">
       <c r="A455">
-        <v>2047878479611</v>
+        <v>2047878479642</v>
       </c>
       <c r="B455">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="456">
       <c r="A456">
-        <v>2047878479642</v>
+        <v>2047878479666</v>
       </c>
       <c r="B456">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="457">
       <c r="A457">
-        <v>2047878479666</v>
+        <v>2047878479697</v>
       </c>
       <c r="B457">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="458">
       <c r="A458">
-        <v>2047878479697</v>
+        <v>2047967094176</v>
       </c>
       <c r="B458">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="459">
       <c r="A459">
-        <v>2047967094176</v>
+        <v>2047967094213</v>
       </c>
       <c r="B459">
         <v>0</v>
@@ -4073,7 +4073,7 @@
     </row>
     <row r="460">
       <c r="A460">
-        <v>2047967094213</v>
+        <v>2047967094268</v>
       </c>
       <c r="B460">
         <v>0</v>
@@ -4081,7 +4081,7 @@
     </row>
     <row r="461">
       <c r="A461">
-        <v>2047967094268</v>
+        <v>2047967094282</v>
       </c>
       <c r="B461">
         <v>0</v>
@@ -4089,7 +4089,7 @@
     </row>
     <row r="462">
       <c r="A462">
-        <v>2047967094282</v>
+        <v>2047967094305</v>
       </c>
       <c r="B462">
         <v>0</v>
@@ -4097,15 +4097,15 @@
     </row>
     <row r="463">
       <c r="A463">
-        <v>2047967094305</v>
+        <v>2047967094336</v>
       </c>
       <c r="B463">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="464">
       <c r="A464">
-        <v>2047967094336</v>
+        <v>2047970232299</v>
       </c>
       <c r="B464">
         <v>5</v>
@@ -4113,7 +4113,7 @@
     </row>
     <row r="465">
       <c r="A465">
-        <v>2047970232299</v>
+        <v>2047970232305</v>
       </c>
       <c r="B465">
         <v>5</v>
@@ -4121,7 +4121,7 @@
     </row>
     <row r="466">
       <c r="A466">
-        <v>2047970232305</v>
+        <v>2047970232329</v>
       </c>
       <c r="B466">
         <v>5</v>
@@ -4129,7 +4129,7 @@
     </row>
     <row r="467">
       <c r="A467">
-        <v>2047970232329</v>
+        <v>2047970232343</v>
       </c>
       <c r="B467">
         <v>5</v>
@@ -4137,7 +4137,7 @@
     </row>
     <row r="468">
       <c r="A468">
-        <v>2047970232343</v>
+        <v>2047970232367</v>
       </c>
       <c r="B468">
         <v>5</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="469">
       <c r="A469">
-        <v>2047970232367</v>
+        <v>2047970232381</v>
       </c>
       <c r="B469">
         <v>5</v>
@@ -4153,7 +4153,7 @@
     </row>
     <row r="470">
       <c r="A470">
-        <v>2047970232381</v>
+        <v>2047970232404</v>
       </c>
       <c r="B470">
         <v>5</v>
@@ -4161,7 +4161,7 @@
     </row>
     <row r="471">
       <c r="A471">
-        <v>2047970232404</v>
+        <v>2047970232411</v>
       </c>
       <c r="B471">
         <v>5</v>
@@ -4169,7 +4169,7 @@
     </row>
     <row r="472">
       <c r="A472">
-        <v>2047970232411</v>
+        <v>2047970232435</v>
       </c>
       <c r="B472">
         <v>5</v>
@@ -4177,7 +4177,7 @@
     </row>
     <row r="473">
       <c r="A473">
-        <v>2047970232435</v>
+        <v>2047970232459</v>
       </c>
       <c r="B473">
         <v>5</v>
@@ -4185,23 +4185,23 @@
     </row>
     <row r="474">
       <c r="A474">
-        <v>2047970232459</v>
+        <v>2047970232466</v>
       </c>
       <c r="B474">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
       <c r="A475">
-        <v>2047970232466</v>
+        <v>2047970232480</v>
       </c>
       <c r="B475">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="476">
       <c r="A476">
-        <v>2047970232480</v>
+        <v>2047970232503</v>
       </c>
       <c r="B476">
         <v>5</v>
@@ -4209,7 +4209,7 @@
     </row>
     <row r="477">
       <c r="A477">
-        <v>2047970232503</v>
+        <v>2047970232534</v>
       </c>
       <c r="B477">
         <v>5</v>
@@ -4217,7 +4217,7 @@
     </row>
     <row r="478">
       <c r="A478">
-        <v>2047970232534</v>
+        <v>2047970232541</v>
       </c>
       <c r="B478">
         <v>5</v>
@@ -4225,7 +4225,7 @@
     </row>
     <row r="479">
       <c r="A479">
-        <v>2047970232541</v>
+        <v>2047970232572</v>
       </c>
       <c r="B479">
         <v>5</v>
@@ -4233,7 +4233,7 @@
     </row>
     <row r="480">
       <c r="A480">
-        <v>2047970232572</v>
+        <v>2047970232589</v>
       </c>
       <c r="B480">
         <v>5</v>
@@ -4241,7 +4241,7 @@
     </row>
     <row r="481">
       <c r="A481">
-        <v>2047970232589</v>
+        <v>2047970232596</v>
       </c>
       <c r="B481">
         <v>5</v>
@@ -4249,7 +4249,7 @@
     </row>
     <row r="482">
       <c r="A482">
-        <v>2047970232596</v>
+        <v>2047970232619</v>
       </c>
       <c r="B482">
         <v>5</v>
@@ -4257,7 +4257,7 @@
     </row>
     <row r="483">
       <c r="A483">
-        <v>2047970232619</v>
+        <v>2047970232633</v>
       </c>
       <c r="B483">
         <v>5</v>
@@ -4265,7 +4265,7 @@
     </row>
     <row r="484">
       <c r="A484">
-        <v>2047970232633</v>
+        <v>2047970232657</v>
       </c>
       <c r="B484">
         <v>5</v>
@@ -4273,7 +4273,7 @@
     </row>
     <row r="485">
       <c r="A485">
-        <v>2047970232657</v>
+        <v>2047970232664</v>
       </c>
       <c r="B485">
         <v>5</v>
@@ -4281,7 +4281,7 @@
     </row>
     <row r="486">
       <c r="A486">
-        <v>2047970232664</v>
+        <v>2047970232695</v>
       </c>
       <c r="B486">
         <v>5</v>
@@ -4289,7 +4289,7 @@
     </row>
     <row r="487">
       <c r="A487">
-        <v>2047970232695</v>
+        <v>2047970232701</v>
       </c>
       <c r="B487">
         <v>5</v>
@@ -4297,7 +4297,7 @@
     </row>
     <row r="488">
       <c r="A488">
-        <v>2047970232701</v>
+        <v>2047970232725</v>
       </c>
       <c r="B488">
         <v>5</v>
@@ -4305,7 +4305,7 @@
     </row>
     <row r="489">
       <c r="A489">
-        <v>2047970232725</v>
+        <v>2047970232732</v>
       </c>
       <c r="B489">
         <v>5</v>
@@ -4313,7 +4313,7 @@
     </row>
     <row r="490">
       <c r="A490">
-        <v>2047970232732</v>
+        <v>2047970232749</v>
       </c>
       <c r="B490">
         <v>5</v>
@@ -4321,7 +4321,7 @@
     </row>
     <row r="491">
       <c r="A491">
-        <v>2047970232749</v>
+        <v>2047970232763</v>
       </c>
       <c r="B491">
         <v>5</v>
@@ -4329,7 +4329,7 @@
     </row>
     <row r="492">
       <c r="A492">
-        <v>2047970232763</v>
+        <v>2047970233050</v>
       </c>
       <c r="B492">
         <v>5</v>
@@ -4337,7 +4337,7 @@
     </row>
     <row r="493">
       <c r="A493">
-        <v>2047970233050</v>
+        <v>2047970233067</v>
       </c>
       <c r="B493">
         <v>5</v>
@@ -4345,7 +4345,7 @@
     </row>
     <row r="494">
       <c r="A494">
-        <v>2047970233067</v>
+        <v>2047970232985</v>
       </c>
       <c r="B494">
         <v>5</v>
@@ -4353,7 +4353,7 @@
     </row>
     <row r="495">
       <c r="A495">
-        <v>2047970232985</v>
+        <v>2047970233012</v>
       </c>
       <c r="B495">
         <v>5</v>
@@ -4361,7 +4361,7 @@
     </row>
     <row r="496">
       <c r="A496">
-        <v>2047970233012</v>
+        <v>2047970233029</v>
       </c>
       <c r="B496">
         <v>5</v>
@@ -4369,7 +4369,7 @@
     </row>
     <row r="497">
       <c r="A497">
-        <v>2047970233029</v>
+        <v>2047970233036</v>
       </c>
       <c r="B497">
         <v>5</v>
@@ -4377,7 +4377,7 @@
     </row>
     <row r="498">
       <c r="A498">
-        <v>2047970233036</v>
+        <v>2047983960783</v>
       </c>
       <c r="B498">
         <v>5</v>
@@ -4385,23 +4385,23 @@
     </row>
     <row r="499">
       <c r="A499">
-        <v>2047983960783</v>
+        <v>2047983960790</v>
       </c>
       <c r="B499">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500">
-        <v>2047983960790</v>
+        <v>2047983960820</v>
       </c>
       <c r="B500">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="501">
       <c r="A501">
-        <v>2047983960820</v>
+        <v>2047983960837</v>
       </c>
       <c r="B501">
         <v>5</v>
@@ -4409,15 +4409,15 @@
     </row>
     <row r="502">
       <c r="A502">
-        <v>2047983960837</v>
+        <v>2047983960844</v>
       </c>
       <c r="B502">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
       <c r="A503">
-        <v>2047983960844</v>
+        <v>2047983960868</v>
       </c>
       <c r="B503">
         <v>0</v>
@@ -4425,31 +4425,31 @@
     </row>
     <row r="504">
       <c r="A504">
-        <v>2047983960868</v>
+        <v>2047983960875</v>
       </c>
       <c r="B504">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505">
       <c r="A505">
-        <v>2047983960875</v>
+        <v>2047983960912</v>
       </c>
       <c r="B505">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="506">
       <c r="A506">
-        <v>2047983960912</v>
+        <v>2047983960936</v>
       </c>
       <c r="B506">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="507">
       <c r="A507">
-        <v>2047983960936</v>
+        <v>2047983960943</v>
       </c>
       <c r="B507">
         <v>5</v>
@@ -4457,23 +4457,23 @@
     </row>
     <row r="508">
       <c r="A508">
-        <v>2047983960943</v>
+        <v>2047983960967</v>
       </c>
       <c r="B508">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="509">
       <c r="A509">
-        <v>2047983960967</v>
+        <v>2047983960974</v>
       </c>
       <c r="B509">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="510">
       <c r="A510">
-        <v>2047983960974</v>
+        <v>2047983960981</v>
       </c>
       <c r="B510">
         <v>5</v>
@@ -4481,7 +4481,7 @@
     </row>
     <row r="511">
       <c r="A511">
-        <v>2047983960981</v>
+        <v>2047983961001</v>
       </c>
       <c r="B511">
         <v>5</v>
@@ -4489,7 +4489,7 @@
     </row>
     <row r="512">
       <c r="A512">
-        <v>2047983961001</v>
+        <v>2047983961018</v>
       </c>
       <c r="B512">
         <v>5</v>
@@ -4497,7 +4497,7 @@
     </row>
     <row r="513">
       <c r="A513">
-        <v>2047983961018</v>
+        <v>2047983961032</v>
       </c>
       <c r="B513">
         <v>5</v>
@@ -4505,7 +4505,7 @@
     </row>
     <row r="514">
       <c r="A514">
-        <v>2047983961032</v>
+        <v>2047983961049</v>
       </c>
       <c r="B514">
         <v>5</v>
@@ -4513,7 +4513,7 @@
     </row>
     <row r="515">
       <c r="A515">
-        <v>2047983961049</v>
+        <v>2047983961070</v>
       </c>
       <c r="B515">
         <v>5</v>
@@ -4521,23 +4521,23 @@
     </row>
     <row r="516">
       <c r="A516">
-        <v>2047983961070</v>
+        <v>2047983961094</v>
       </c>
       <c r="B516">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="517">
       <c r="A517">
-        <v>2047983961094</v>
+        <v>2047983961124</v>
       </c>
       <c r="B517">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="518">
       <c r="A518">
-        <v>2047983961124</v>
+        <v>2047983961148</v>
       </c>
       <c r="B518">
         <v>5</v>
@@ -4545,7 +4545,7 @@
     </row>
     <row r="519">
       <c r="A519">
-        <v>2047983961148</v>
+        <v>2047983961179</v>
       </c>
       <c r="B519">
         <v>5</v>
@@ -4553,7 +4553,7 @@
     </row>
     <row r="520">
       <c r="A520">
-        <v>2047983961179</v>
+        <v>2047983961223</v>
       </c>
       <c r="B520">
         <v>5</v>
@@ -4561,7 +4561,7 @@
     </row>
     <row r="521">
       <c r="A521">
-        <v>2047983961223</v>
+        <v>2047983961230</v>
       </c>
       <c r="B521">
         <v>5</v>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="522">
       <c r="A522">
-        <v>2047983961230</v>
+        <v>2047985137657</v>
       </c>
       <c r="B522">
         <v>5</v>
@@ -4577,7 +4577,7 @@
     </row>
     <row r="523">
       <c r="A523">
-        <v>2047985137657</v>
+        <v>2047985137701</v>
       </c>
       <c r="B523">
         <v>5</v>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="524">
       <c r="A524">
-        <v>2047985137701</v>
+        <v>2047985137725</v>
       </c>
       <c r="B524">
         <v>5</v>
@@ -4593,7 +4593,7 @@
     </row>
     <row r="525">
       <c r="A525">
-        <v>2047985137725</v>
+        <v>2047985137756</v>
       </c>
       <c r="B525">
         <v>5</v>
@@ -4601,7 +4601,7 @@
     </row>
     <row r="526">
       <c r="A526">
-        <v>2047985137756</v>
+        <v>2047985137770</v>
       </c>
       <c r="B526">
         <v>5</v>
@@ -4609,15 +4609,15 @@
     </row>
     <row r="527">
       <c r="A527">
-        <v>2047985137770</v>
+        <v>2047985137787</v>
       </c>
       <c r="B527">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528">
       <c r="A528">
-        <v>2047985137787</v>
+        <v>2047985137800</v>
       </c>
       <c r="B528">
         <v>0</v>
@@ -4625,39 +4625,39 @@
     </row>
     <row r="529">
       <c r="A529">
-        <v>2047985137800</v>
+        <v>2047985137848</v>
       </c>
       <c r="B529">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="530">
       <c r="A530">
-        <v>2047985137848</v>
+        <v>2047985137985</v>
       </c>
       <c r="B530">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531">
       <c r="A531">
-        <v>2047985137985</v>
+        <v>2047985138005</v>
       </c>
       <c r="B531">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="532">
       <c r="A532">
-        <v>2047985138005</v>
+        <v>2047985137435</v>
       </c>
       <c r="B532">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
       <c r="A533">
-        <v>2047985137435</v>
+        <v>2047985137442</v>
       </c>
       <c r="B533">
         <v>0</v>
@@ -4665,15 +4665,15 @@
     </row>
     <row r="534">
       <c r="A534">
-        <v>2047985137442</v>
+        <v>2047985137466</v>
       </c>
       <c r="B534">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="535">
       <c r="A535">
-        <v>2047985137466</v>
+        <v>2047985137480</v>
       </c>
       <c r="B535">
         <v>5</v>
@@ -4681,7 +4681,7 @@
     </row>
     <row r="536">
       <c r="A536">
-        <v>2047985137480</v>
+        <v>2047985137503</v>
       </c>
       <c r="B536">
         <v>5</v>
@@ -4689,7 +4689,7 @@
     </row>
     <row r="537">
       <c r="A537">
-        <v>2047985137503</v>
+        <v>2047985137527</v>
       </c>
       <c r="B537">
         <v>5</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="538">
       <c r="A538">
-        <v>2047985137527</v>
+        <v>2047985137534</v>
       </c>
       <c r="B538">
         <v>5</v>
@@ -4705,15 +4705,15 @@
     </row>
     <row r="539">
       <c r="A539">
-        <v>2047985137534</v>
+        <v>2047985137565</v>
       </c>
       <c r="B539">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
       <c r="A540">
-        <v>2047985137565</v>
+        <v>2047985137572</v>
       </c>
       <c r="B540">
         <v>0</v>
@@ -4721,15 +4721,15 @@
     </row>
     <row r="541">
       <c r="A541">
-        <v>2047985137572</v>
+        <v>2047985137596</v>
       </c>
       <c r="B541">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="542">
       <c r="A542">
-        <v>2047985137596</v>
+        <v>2047985137619</v>
       </c>
       <c r="B542">
         <v>5</v>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="543">
       <c r="A543">
-        <v>2047985137619</v>
+        <v>2047985137626</v>
       </c>
       <c r="B543">
         <v>5</v>
@@ -4745,7 +4745,7 @@
     </row>
     <row r="544">
       <c r="A544">
-        <v>2047985137626</v>
+        <v>2047985137633</v>
       </c>
       <c r="B544">
         <v>5</v>
@@ -4753,23 +4753,23 @@
     </row>
     <row r="545">
       <c r="A545">
-        <v>2047985137633</v>
+        <v>2047985138098</v>
       </c>
       <c r="B545">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546">
       <c r="A546">
-        <v>2047985138098</v>
+        <v>2047985137350</v>
       </c>
       <c r="B546">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
       <c r="A547">
-        <v>2047985137350</v>
+        <v>2047985137398</v>
       </c>
       <c r="B547">
         <v>0</v>
@@ -4777,15 +4777,15 @@
     </row>
     <row r="548">
       <c r="A548">
-        <v>2047985137398</v>
+        <v>2047985137428</v>
       </c>
       <c r="B548">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="549">
       <c r="A549">
-        <v>2047985137428</v>
+        <v>2047983960523</v>
       </c>
       <c r="B549">
         <v>5</v>
@@ -4793,15 +4793,15 @@
     </row>
     <row r="550">
       <c r="A550">
-        <v>2047983960523</v>
+        <v>2047983960585</v>
       </c>
       <c r="B550">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551">
       <c r="A551">
-        <v>2047983960585</v>
+        <v>2047983960592</v>
       </c>
       <c r="B551">
         <v>0</v>
@@ -4809,15 +4809,15 @@
     </row>
     <row r="552">
       <c r="A552">
-        <v>2047983960592</v>
+        <v>2047983960615</v>
       </c>
       <c r="B552">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553">
       <c r="A553">
-        <v>2047983960615</v>
+        <v>2047983960646</v>
       </c>
       <c r="B553">
         <v>5</v>
@@ -4825,7 +4825,7 @@
     </row>
     <row r="554">
       <c r="A554">
-        <v>2047983960646</v>
+        <v>2047983960660</v>
       </c>
       <c r="B554">
         <v>5</v>
@@ -4833,31 +4833,31 @@
     </row>
     <row r="555">
       <c r="A555">
-        <v>2047983960660</v>
+        <v>2047983960684</v>
       </c>
       <c r="B555">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556">
-        <v>2047983960684</v>
+        <v>2047983960691</v>
       </c>
       <c r="B556">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557">
       <c r="A557">
-        <v>2047983960691</v>
+        <v>2047983960721</v>
       </c>
       <c r="B557">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
       <c r="A558">
-        <v>2047983960721</v>
+        <v>2043802980185</v>
       </c>
       <c r="B558">
         <v>0</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="559">
       <c r="A559">
-        <v>2043802980185</v>
+        <v>2043802980055</v>
       </c>
       <c r="B559">
         <v>0</v>
@@ -4873,7 +4873,7 @@
     </row>
     <row r="560">
       <c r="A560">
-        <v>2043802980055</v>
+        <v>2043802980239</v>
       </c>
       <c r="B560">
         <v>0</v>
@@ -4881,15 +4881,15 @@
     </row>
     <row r="561">
       <c r="A561">
-        <v>2043802980239</v>
+        <v>2048416054383</v>
       </c>
       <c r="B561">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="562">
       <c r="A562">
-        <v>2048416054383</v>
+        <v>2048416054406</v>
       </c>
       <c r="B562">
         <v>5</v>
@@ -4897,7 +4897,7 @@
     </row>
     <row r="563">
       <c r="A563">
-        <v>2048416054406</v>
+        <v>2048416054277</v>
       </c>
       <c r="B563">
         <v>5</v>
@@ -4905,7 +4905,7 @@
     </row>
     <row r="564">
       <c r="A564">
-        <v>2048416054277</v>
+        <v>2048416054284</v>
       </c>
       <c r="B564">
         <v>5</v>
@@ -4913,7 +4913,7 @@
     </row>
     <row r="565">
       <c r="A565">
-        <v>2048416054284</v>
+        <v>2048416054291</v>
       </c>
       <c r="B565">
         <v>5</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="566">
       <c r="A566">
-        <v>2048416054291</v>
+        <v>2048416054307</v>
       </c>
       <c r="B566">
         <v>5</v>
@@ -4929,15 +4929,15 @@
     </row>
     <row r="567">
       <c r="A567">
-        <v>2048416054307</v>
+        <v>2048416054314</v>
       </c>
       <c r="B567">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
       <c r="A568">
-        <v>2048416054314</v>
+        <v>2048416054321</v>
       </c>
       <c r="B568">
         <v>0</v>
@@ -4945,15 +4945,15 @@
     </row>
     <row r="569">
       <c r="A569">
-        <v>2048416054321</v>
+        <v>2048416054345</v>
       </c>
       <c r="B569">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="570">
       <c r="A570">
-        <v>2048416054345</v>
+        <v>2048416054352</v>
       </c>
       <c r="B570">
         <v>5</v>
@@ -4961,31 +4961,23 @@
     </row>
     <row r="571">
       <c r="A571">
-        <v>2048416054352</v>
+        <v>2048416054369</v>
       </c>
       <c r="B571">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572">
       <c r="A572">
-        <v>2048416054369</v>
+        <v>2048416054376</v>
       </c>
       <c r="B572">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573">
-        <v>2048416054376</v>
-      </c>
-      <c r="B573">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B573"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B572"/>
   </ignoredErrors>
 </worksheet>
 </file>